--- a/Data/2022_Carb_data/Leaf_all_additional_analysis.xlsx
+++ b/Data/2022_Carb_data/Leaf_all_additional_analysis.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ximinpiao/Documents/GitHub/UTR-Soybean-BioCro/Data/2022_Carb_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4D133D-1AAF-8542-9926-D8171784AF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2073A30F-5B63-3647-87C3-AF4B9189B628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10340" yWindow="600" windowWidth="18460" windowHeight="16080" activeTab="1" xr2:uid="{91BF93B6-657D-F94F-A5FA-7F2899DF2E06}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="4" xr2:uid="{91BF93B6-657D-F94F-A5FA-7F2899DF2E06}"/>
   </bookViews>
   <sheets>
-    <sheet name="og" sheetId="1" r:id="rId1"/>
-    <sheet name="glucose" sheetId="2" r:id="rId2"/>
-    <sheet name="C" sheetId="4" r:id="rId3"/>
-    <sheet name="DM" sheetId="3" r:id="rId4"/>
+    <sheet name="og" sheetId="5" r:id="rId1"/>
+    <sheet name="og-wrong-version" sheetId="1" r:id="rId2"/>
+    <sheet name="glucose" sheetId="2" r:id="rId3"/>
+    <sheet name="C" sheetId="4" r:id="rId4"/>
+    <sheet name="DM" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="40">
   <si>
     <t>Sample ID</t>
   </si>
@@ -301,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,6 +506,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -667,7 +680,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -697,28 +710,47 @@
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="38" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="34" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="38" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="34" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -888,15 +920,51 @@
                     <c:v>DOY</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="11">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -922,10 +990,10 @@
                   <c:v>880.63333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>880.63333333333333</c:v>
+                  <c:v>400.83333333333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>419.27500000000003</c:v>
+                  <c:v>178.29438425249901</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.96666666666667</c:v>
@@ -1009,10 +1077,10 @@
                   <c:v>115.26666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.26666666666667</c:v>
+                  <c:v>109.83333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>111.925</c:v>
+                  <c:v>119.09323653785117</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>131.26666666666668</c:v>
@@ -1333,15 +1401,51 @@
                     <c:v>DOY</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="11">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1367,10 +1471,10 @@
                   <c:v>880.63333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>880.63333333333333</c:v>
+                  <c:v>400.83333333333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>419.27500000000003</c:v>
+                  <c:v>178.29438425249901</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.96666666666667</c:v>
@@ -1454,10 +1558,10 @@
                   <c:v>115.26666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.26666666666667</c:v>
+                  <c:v>109.83333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>111.925</c:v>
+                  <c:v>119.09323653785117</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>131.26666666666668</c:v>
@@ -1737,10 +1841,10 @@
                     <c:v>54.006869752253309</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>54.006869752253309</c:v>
+                    <c:v>37.961340601242881</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>15.039536844262681</c:v>
+                    <c:v>15.466026056423813</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>123.20404283700545</c:v>
@@ -1794,10 +1898,10 @@
                     <c:v>54.006869752253309</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>54.006869752253309</c:v>
+                    <c:v>37.961340601242881</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>15.039536844262681</c:v>
+                    <c:v>15.466026056423813</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>123.20404283700545</c:v>
@@ -1903,15 +2007,51 @@
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="8">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="9">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="10">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="11">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="13">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1937,10 +2077,10 @@
                   <c:v>115.26666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.26666666666667</c:v>
+                  <c:v>109.83333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>111.925</c:v>
+                  <c:v>119.09323653785117</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>131.26666666666668</c:v>
@@ -2028,10 +2168,10 @@
                     <c:v>71.248953208684625</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>71.248953208684625</c:v>
+                    <c:v>138.40651477923043</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>118.87509901853571</c:v>
+                    <c:v>123.53014028695534</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>30.958897482522421</c:v>
@@ -2085,10 +2225,10 @@
                     <c:v>71.248953208684625</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>71.248953208684625</c:v>
+                    <c:v>138.40651477923043</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>118.87509901853571</c:v>
+                    <c:v>123.53014028695534</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>30.958897482522421</c:v>
@@ -2194,15 +2334,51 @@
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="8">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="9">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="10">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="11">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="13">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -2228,10 +2404,10 @@
                   <c:v>880.63333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>880.63333333333333</c:v>
+                  <c:v>400.83333333333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>419.27500000000003</c:v>
+                  <c:v>178.29438425249901</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.96666666666667</c:v>
@@ -2370,15 +2546,51 @@
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="8">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="9">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="10">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="11">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="13">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -2404,10 +2616,10 @@
                   <c:v>0.1157412056096663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1157412056096663</c:v>
+                  <c:v>0.21507832898172324</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.21070218373493974</c:v>
+                  <c:v>0.4004646737525383</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.47692866658592714</c:v>
@@ -2752,10 +2964,10 @@
                     <c:v>0.3240412185135198</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.3240412185135198</c:v>
+                    <c:v>0.22776804360745753</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>9.023722106557619E-2</c:v>
+                    <c:v>9.2796156338542837E-2</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>0.73922425702203265</c:v>
@@ -2809,10 +3021,10 @@
                     <c:v>0.3240412185135198</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.3240412185135198</c:v>
+                    <c:v>0.22776804360745753</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>9.023722106557619E-2</c:v>
+                    <c:v>9.2796156338542837E-2</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>0.73922425702203265</c:v>
@@ -2952,10 +3164,10 @@
                   <c:v>0.6916000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6916000000000001</c:v>
+                  <c:v>0.65900000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.67155000000000009</c:v>
+                  <c:v>0.71455941922710697</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.78759999999999997</c:v>
@@ -3043,10 +3255,10 @@
                     <c:v>0.42749371925210777</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.42749371925210777</c:v>
+                    <c:v>0.83043908867538285</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0.71325059411121439</c:v>
+                    <c:v>0.74118084172173204</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>0.18575338489513452</c:v>
@@ -3100,10 +3312,10 @@
                     <c:v>0.42749371925210777</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.42749371925210777</c:v>
+                    <c:v>0.83043908867538285</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0.71325059411121439</c:v>
+                    <c:v>0.74118084172173204</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>0.18575338489513452</c:v>
@@ -3243,10 +3455,10 @@
                   <c:v>5.2838000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.2838000000000003</c:v>
+                  <c:v>2.4049999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5156500000000004</c:v>
+                  <c:v>1.069766305514994</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.8637999999999999</c:v>
@@ -3419,10 +3631,10 @@
                   <c:v>0.1157412056096663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1157412056096663</c:v>
+                  <c:v>0.21507832898172324</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.21070218373493974</c:v>
+                  <c:v>0.40046467375253836</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.47692866658592714</c:v>
@@ -3807,15 +4019,51 @@
                     <c:v>DOY</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="11">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -3841,10 +4089,10 @@
                   <c:v>880.63333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>880.63333333333333</c:v>
+                  <c:v>400.83333333333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>419.27500000000003</c:v>
+                  <c:v>178.29438425249901</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.96666666666667</c:v>
@@ -3928,10 +4176,10 @@
                   <c:v>115.26666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.26666666666667</c:v>
+                  <c:v>109.83333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>111.925</c:v>
+                  <c:v>119.09323653785117</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>131.26666666666668</c:v>
@@ -4252,15 +4500,51 @@
                     <c:v>DOY</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>186-197</c:v>
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>186</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>187</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>187</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>209</c:v>
                   </c:pt>
+                  <c:pt idx="10">
+                    <c:v>209</c:v>
+                  </c:pt>
                   <c:pt idx="11">
                     <c:v>236</c:v>
                   </c:pt>
+                  <c:pt idx="12">
+                    <c:v>236</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>236</c:v>
+                  </c:pt>
                   <c:pt idx="14">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>258</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
                     <c:v>258</c:v>
                   </c:pt>
                 </c:lvl>
@@ -4286,10 +4570,10 @@
                   <c:v>880.63333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>880.63333333333333</c:v>
+                  <c:v>400.83333333333331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>419.27500000000003</c:v>
+                  <c:v>178.29438425249901</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.96666666666667</c:v>
@@ -4373,10 +4657,10 @@
                   <c:v>115.26666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.26666666666667</c:v>
+                  <c:v>109.83333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>111.925</c:v>
+                  <c:v>119.09323653785117</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>131.26666666666668</c:v>
@@ -4656,10 +4940,10 @@
                     <c:v>9.7212365554055928</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>9.7212365554055928</c:v>
+                    <c:v>6.8330413082237165</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>2.707116631967279</c:v>
+                    <c:v>2.7838846901562877</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>22.17672771066098</c:v>
@@ -4713,10 +4997,10 @@
                     <c:v>9.7212365554055928</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>9.7212365554055928</c:v>
+                    <c:v>6.8330413082237165</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>2.707116631967279</c:v>
+                    <c:v>2.7838846901562877</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>22.17672771066098</c:v>
@@ -4856,10 +5140,10 @@
                   <c:v>20.748000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.748000000000001</c:v>
+                  <c:v>19.77</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.1465</c:v>
+                  <c:v>21.436782576813208</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>23.628</c:v>
@@ -4947,10 +5231,10 @@
                     <c:v>12.824811577563233</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>12.824811577563233</c:v>
+                    <c:v>24.913172660261477</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>21.397517823336422</c:v>
+                    <c:v>22.235425251651964</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>5.5726015468540364</c:v>
@@ -5004,10 +5288,10 @@
                     <c:v>12.824811577563233</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>12.824811577563233</c:v>
+                    <c:v>24.913172660261477</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>21.397517823336422</c:v>
+                    <c:v>22.235425251651964</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>5.5726015468540364</c:v>
@@ -5147,10 +5431,10 @@
                   <c:v>158.51400000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>158.51400000000001</c:v>
+                  <c:v>72.149999999999991</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.469499999999996</c:v>
+                  <c:v>32.092989165449822</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>25.913999999999998</c:v>
@@ -5323,10 +5607,10 @@
                   <c:v>0.1157412056096663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1157412056096663</c:v>
+                  <c:v>0.21507832898172327</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.21070218373493976</c:v>
+                  <c:v>0.4004646737525383</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.47692866658592709</c:v>
@@ -10073,9 +10357,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA53049-B4D8-AE45-9104-589E80333CE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDD86B5-5D6E-4742-8844-A62DE10B62E2}">
   <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -10519,46 +10808,46 @@
         <v>27</v>
       </c>
       <c r="H6">
-        <v>114.8</v>
+        <v>124.2</v>
       </c>
       <c r="I6">
-        <v>961.9</v>
+        <v>305.60000000000002</v>
       </c>
       <c r="J6">
-        <v>118.4</v>
+        <v>118.2</v>
       </c>
       <c r="K6">
-        <v>804.3</v>
+        <v>474.6</v>
       </c>
       <c r="L6">
-        <v>112.3</v>
+        <v>94.8</v>
       </c>
       <c r="M6">
-        <v>851.1</v>
+        <v>559.6</v>
       </c>
       <c r="N6">
-        <v>118.7</v>
+        <v>110.5</v>
       </c>
       <c r="O6">
-        <v>828.9</v>
+        <v>337.3</v>
       </c>
       <c r="P6">
-        <v>1076.8</v>
+        <v>429.9</v>
       </c>
       <c r="Q6">
-        <v>922.7</v>
+        <v>592.79999999999995</v>
       </c>
       <c r="R6">
-        <v>963.4</v>
+        <v>654.29999999999995</v>
       </c>
       <c r="S6">
-        <v>947.6</v>
+        <v>447.8</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6">
         <v>1</v>
@@ -10567,16 +10856,16 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y6">
-        <v>995.9</v>
+        <v>531.20000000000005</v>
       </c>
       <c r="Z6">
-        <v>57.5</v>
+        <v>95.1</v>
       </c>
       <c r="AA6" s="3">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="AC6" s="4"/>
     </row>
@@ -10602,65 +10891,73 @@
       <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="H7">
-        <v>124.2</v>
-      </c>
-      <c r="I7">
-        <v>305.60000000000002</v>
-      </c>
-      <c r="J7">
-        <v>118.2</v>
-      </c>
-      <c r="K7">
-        <v>474.6</v>
-      </c>
-      <c r="L7">
-        <v>94.8</v>
-      </c>
-      <c r="M7">
-        <v>559.6</v>
-      </c>
-      <c r="N7">
-        <v>110.5</v>
-      </c>
-      <c r="O7">
-        <v>337.3</v>
-      </c>
-      <c r="P7">
-        <v>429.9</v>
-      </c>
-      <c r="Q7">
-        <v>592.79999999999995</v>
-      </c>
-      <c r="R7">
-        <v>654.29999999999995</v>
-      </c>
-      <c r="S7">
-        <v>447.8</v>
+      <c r="H7" s="4">
+        <v>128.894277241759</v>
+      </c>
+      <c r="I7" s="4">
+        <v>201.03869994973999</v>
+      </c>
+      <c r="J7" s="4">
+        <v>98.082383338050704</v>
+      </c>
+      <c r="K7" s="4">
+        <v>282.28948157027298</v>
+      </c>
+      <c r="L7" s="4">
+        <v>129.08580316799001</v>
+      </c>
+      <c r="M7" s="4">
+        <v>229.849355489983</v>
+      </c>
+      <c r="N7" s="4">
+        <v>120.31048240360499</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <f>H7+I7</f>
+        <v>329.93297719149899</v>
+      </c>
+      <c r="Q7" s="4">
+        <f>J7+K7</f>
+        <v>380.37186490832369</v>
+      </c>
+      <c r="R7" s="4">
+        <f>L7+M7</f>
+        <v>358.93515865797303</v>
+      </c>
+      <c r="S7" s="4">
+        <f>M7+N7</f>
+        <v>350.15983789358802</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <v>1</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>4</v>
-      </c>
-      <c r="Y7">
-        <v>531.20000000000005</v>
-      </c>
-      <c r="Z7">
-        <v>95.1</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0.18</v>
+        <f>SUM(T7:W7)</f>
+        <v>2</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>(P7*T7+Q7*U7+R7*V7+S7*W7)/X7</f>
+        <v>344.43406792473604</v>
+      </c>
+      <c r="Z7" s="4">
+        <f>SQRT((((P7-Y7)^2)*T7+((Q7-Y7)^2)*U7+((R7-Y7)^2)*V7+((S7-Y7)^2)*W7)/X7)</f>
+        <v>14.501090733237021</v>
+      </c>
+      <c r="AA7" s="39">
+        <f>Z7/Y7</f>
+        <v>4.2101209153345788E-2</v>
       </c>
       <c r="AC7" s="4"/>
     </row>
@@ -11510,6 +11807,1443 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA53049-B4D8-AE45-9104-589E80333CE0}">
+  <dimension ref="A1:AC17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>37196</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C2">
+        <v>186</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>186.45833300000001</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44747</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>237.7</v>
+      </c>
+      <c r="I2">
+        <v>298.2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>300.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>242.1</v>
+      </c>
+      <c r="O2">
+        <v>305.10000000000002</v>
+      </c>
+      <c r="P2">
+        <v>535.9</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>300.8</v>
+      </c>
+      <c r="S2">
+        <v>547.20000000000005</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <v>541.5</v>
+      </c>
+      <c r="Z2">
+        <v>5.7</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="AC2" s="4"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>37561</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C3">
+        <v>186</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>186.58333300000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44747</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>181.6</v>
+      </c>
+      <c r="I3">
+        <v>245.1</v>
+      </c>
+      <c r="J3">
+        <v>143.5</v>
+      </c>
+      <c r="K3">
+        <v>573</v>
+      </c>
+      <c r="L3">
+        <v>141.1</v>
+      </c>
+      <c r="M3">
+        <v>354.8</v>
+      </c>
+      <c r="N3">
+        <v>112.8</v>
+      </c>
+      <c r="O3">
+        <v>355.8</v>
+      </c>
+      <c r="P3">
+        <v>426.7</v>
+      </c>
+      <c r="Q3">
+        <v>716.5</v>
+      </c>
+      <c r="R3">
+        <v>495.8</v>
+      </c>
+      <c r="S3">
+        <v>468.6</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>4</v>
+      </c>
+      <c r="Y3">
+        <v>526.9</v>
+      </c>
+      <c r="Z3">
+        <v>112.2</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="AC3" s="4"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>37926</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C4">
+        <v>186</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>186.70833300000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44747</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>140.69999999999999</v>
+      </c>
+      <c r="I4">
+        <v>335.6</v>
+      </c>
+      <c r="J4">
+        <v>185.6</v>
+      </c>
+      <c r="K4">
+        <v>924.5</v>
+      </c>
+      <c r="L4">
+        <v>121.6</v>
+      </c>
+      <c r="M4">
+        <v>381.6</v>
+      </c>
+      <c r="N4">
+        <v>125.5</v>
+      </c>
+      <c r="O4">
+        <v>914.6</v>
+      </c>
+      <c r="P4">
+        <v>476.3</v>
+      </c>
+      <c r="Q4">
+        <v>1110</v>
+      </c>
+      <c r="R4">
+        <v>503.1</v>
+      </c>
+      <c r="S4">
+        <v>1040.0999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>1075.0999999999999</v>
+      </c>
+      <c r="Z4">
+        <v>35</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="AC4" s="4"/>
+    </row>
+    <row r="5" spans="1:29" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29">
+        <v>38292</v>
+      </c>
+      <c r="B5" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C5" s="31">
+        <v>186</v>
+      </c>
+      <c r="D5" s="31">
+        <v>20</v>
+      </c>
+      <c r="E5" s="31">
+        <v>186.83333300000001</v>
+      </c>
+      <c r="F5" s="29">
+        <v>44747</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="31">
+        <v>114.8</v>
+      </c>
+      <c r="I5" s="31">
+        <v>961.9</v>
+      </c>
+      <c r="J5" s="31">
+        <v>118.4</v>
+      </c>
+      <c r="K5" s="31">
+        <v>804.3</v>
+      </c>
+      <c r="L5" s="31">
+        <v>112.3</v>
+      </c>
+      <c r="M5" s="31">
+        <v>851.1</v>
+      </c>
+      <c r="N5" s="31">
+        <v>118.7</v>
+      </c>
+      <c r="O5" s="31">
+        <v>828.9</v>
+      </c>
+      <c r="P5" s="31">
+        <v>1076.8</v>
+      </c>
+      <c r="Q5" s="31">
+        <v>922.7</v>
+      </c>
+      <c r="R5" s="31">
+        <v>963.4</v>
+      </c>
+      <c r="S5" s="31">
+        <v>947.6</v>
+      </c>
+      <c r="T5" s="31">
+        <v>1</v>
+      </c>
+      <c r="U5" s="31">
+        <v>0</v>
+      </c>
+      <c r="V5" s="31">
+        <v>1</v>
+      </c>
+      <c r="W5" s="31">
+        <v>1</v>
+      </c>
+      <c r="X5" s="31">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="31">
+        <v>995.9</v>
+      </c>
+      <c r="Z5" s="31">
+        <v>57.5</v>
+      </c>
+      <c r="AA5" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="AC5" s="33"/>
+    </row>
+    <row r="6" spans="1:29" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="29">
+        <v>38657</v>
+      </c>
+      <c r="B6" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C6" s="31">
+        <v>186</v>
+      </c>
+      <c r="D6" s="31">
+        <v>23</v>
+      </c>
+      <c r="E6" s="31">
+        <v>186.95833300000001</v>
+      </c>
+      <c r="F6" s="29">
+        <v>44747</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="31">
+        <v>114.8</v>
+      </c>
+      <c r="I6" s="31">
+        <v>961.9</v>
+      </c>
+      <c r="J6" s="31">
+        <v>118.4</v>
+      </c>
+      <c r="K6" s="31">
+        <v>804.3</v>
+      </c>
+      <c r="L6" s="31">
+        <v>112.3</v>
+      </c>
+      <c r="M6" s="31">
+        <v>851.1</v>
+      </c>
+      <c r="N6" s="31">
+        <v>118.7</v>
+      </c>
+      <c r="O6" s="31">
+        <v>828.9</v>
+      </c>
+      <c r="P6" s="31">
+        <v>1076.8</v>
+      </c>
+      <c r="Q6" s="31">
+        <v>922.7</v>
+      </c>
+      <c r="R6" s="31">
+        <v>963.4</v>
+      </c>
+      <c r="S6" s="31">
+        <v>947.6</v>
+      </c>
+      <c r="T6" s="31">
+        <v>1</v>
+      </c>
+      <c r="U6" s="31">
+        <v>0</v>
+      </c>
+      <c r="V6" s="31">
+        <v>1</v>
+      </c>
+      <c r="W6" s="31">
+        <v>1</v>
+      </c>
+      <c r="X6" s="31">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="31">
+        <v>995.9</v>
+      </c>
+      <c r="Z6" s="31">
+        <v>57.5</v>
+      </c>
+      <c r="AA6" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>39022</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C7">
+        <v>187</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>187.08333300000001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44748</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>124.2</v>
+      </c>
+      <c r="I7">
+        <v>305.60000000000002</v>
+      </c>
+      <c r="J7">
+        <v>118.2</v>
+      </c>
+      <c r="K7">
+        <v>474.6</v>
+      </c>
+      <c r="L7">
+        <v>94.8</v>
+      </c>
+      <c r="M7">
+        <v>559.6</v>
+      </c>
+      <c r="N7">
+        <v>110.5</v>
+      </c>
+      <c r="O7">
+        <v>337.3</v>
+      </c>
+      <c r="P7">
+        <v>429.9</v>
+      </c>
+      <c r="Q7">
+        <v>592.79999999999995</v>
+      </c>
+      <c r="R7">
+        <v>654.29999999999995</v>
+      </c>
+      <c r="S7">
+        <v>447.8</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>4</v>
+      </c>
+      <c r="Y7">
+        <v>531.20000000000005</v>
+      </c>
+      <c r="Z7">
+        <v>95.1</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="AC7" s="4"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>39387</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C8">
+        <v>187</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>187.20833300000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44748</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8">
+        <v>125.3</v>
+      </c>
+      <c r="I8">
+        <v>136.1</v>
+      </c>
+      <c r="J8">
+        <v>142</v>
+      </c>
+      <c r="K8">
+        <v>178.1</v>
+      </c>
+      <c r="L8">
+        <v>144.6</v>
+      </c>
+      <c r="M8">
+        <v>-5</v>
+      </c>
+      <c r="N8">
+        <v>126.5</v>
+      </c>
+      <c r="O8">
+        <v>117.7</v>
+      </c>
+      <c r="P8">
+        <v>261.39999999999998</v>
+      </c>
+      <c r="Q8">
+        <v>320.10000000000002</v>
+      </c>
+      <c r="R8">
+        <v>139.5</v>
+      </c>
+      <c r="S8">
+        <v>244.2</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <v>275.2</v>
+      </c>
+      <c r="Z8">
+        <v>32.5</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="AC8" s="4"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>39753</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C9">
+        <v>187</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>187.33333300000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44748</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>107.9</v>
+      </c>
+      <c r="I9">
+        <v>34.4</v>
+      </c>
+      <c r="J9">
+        <v>119.8</v>
+      </c>
+      <c r="K9">
+        <v>22.6</v>
+      </c>
+      <c r="L9">
+        <v>115</v>
+      </c>
+      <c r="M9">
+        <v>44.4</v>
+      </c>
+      <c r="N9">
+        <v>136</v>
+      </c>
+      <c r="O9">
+        <v>-6.4</v>
+      </c>
+      <c r="P9">
+        <v>142.30000000000001</v>
+      </c>
+      <c r="Q9">
+        <v>142.4</v>
+      </c>
+      <c r="R9">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="S9">
+        <v>129.6</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>3</v>
+      </c>
+      <c r="Y9">
+        <v>148</v>
+      </c>
+      <c r="Z9">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="AC9" s="4"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>37197</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C10">
+        <v>209</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>209.33333300000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44770</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10">
+        <v>172.1</v>
+      </c>
+      <c r="I10">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="J10">
+        <v>168.2</v>
+      </c>
+      <c r="K10">
+        <v>12.3</v>
+      </c>
+      <c r="L10">
+        <v>159.80000000000001</v>
+      </c>
+      <c r="M10">
+        <v>1800.9</v>
+      </c>
+      <c r="N10">
+        <v>212.3</v>
+      </c>
+      <c r="O10">
+        <v>104.2</v>
+      </c>
+      <c r="P10">
+        <v>315.89999999999998</v>
+      </c>
+      <c r="Q10">
+        <v>180.6</v>
+      </c>
+      <c r="R10">
+        <v>1960.6</v>
+      </c>
+      <c r="S10">
+        <v>316.5</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+      <c r="Y10">
+        <v>316.2</v>
+      </c>
+      <c r="Z10">
+        <v>0.3</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>37562</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C11">
+        <v>209</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>209.54166699999999</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44770</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>188.2</v>
+      </c>
+      <c r="I11">
+        <v>218.3</v>
+      </c>
+      <c r="J11">
+        <v>246.8</v>
+      </c>
+      <c r="K11">
+        <v>719.6</v>
+      </c>
+      <c r="L11">
+        <v>200.5</v>
+      </c>
+      <c r="M11">
+        <v>894.7</v>
+      </c>
+      <c r="N11">
+        <v>268.3</v>
+      </c>
+      <c r="O11">
+        <v>541.1</v>
+      </c>
+      <c r="P11">
+        <v>406.5</v>
+      </c>
+      <c r="Q11">
+        <v>966.4</v>
+      </c>
+      <c r="R11">
+        <v>1095.2</v>
+      </c>
+      <c r="S11">
+        <v>809.3</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>4</v>
+      </c>
+      <c r="Y11">
+        <v>819.4</v>
+      </c>
+      <c r="Z11">
+        <v>259</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="AC11" s="4"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>37198</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C12">
+        <v>236</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>236.33333300000001</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44797</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>87.8</v>
+      </c>
+      <c r="I12">
+        <v>1032.5</v>
+      </c>
+      <c r="J12">
+        <v>83.4</v>
+      </c>
+      <c r="K12">
+        <v>-3.9</v>
+      </c>
+      <c r="L12">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="M12">
+        <v>628.9</v>
+      </c>
+      <c r="N12">
+        <v>86.7</v>
+      </c>
+      <c r="O12">
+        <v>493.5</v>
+      </c>
+      <c r="P12">
+        <v>1120.3</v>
+      </c>
+      <c r="Q12">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="R12">
+        <v>708</v>
+      </c>
+      <c r="S12">
+        <v>580.20000000000005</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>3</v>
+      </c>
+      <c r="Y12">
+        <v>802.8</v>
+      </c>
+      <c r="Z12">
+        <v>230.4</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AC12" s="4"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>37563</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C13">
+        <v>236</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>236.54166699999999</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44797</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>87.2</v>
+      </c>
+      <c r="I13">
+        <v>1178.8</v>
+      </c>
+      <c r="J13">
+        <v>69.3</v>
+      </c>
+      <c r="K13">
+        <v>1085.5</v>
+      </c>
+      <c r="L13">
+        <v>110</v>
+      </c>
+      <c r="M13">
+        <v>953.4</v>
+      </c>
+      <c r="N13">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="O13">
+        <v>1118.2</v>
+      </c>
+      <c r="P13">
+        <v>1266</v>
+      </c>
+      <c r="Q13">
+        <v>1154.9000000000001</v>
+      </c>
+      <c r="R13">
+        <v>1063.4000000000001</v>
+      </c>
+      <c r="S13">
+        <v>1194.5999999999999</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>4</v>
+      </c>
+      <c r="Y13">
+        <v>1169.7</v>
+      </c>
+      <c r="Z13">
+        <v>73.2</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="AC13" s="4"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>37928</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C14">
+        <v>236</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>236.83333300000001</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44797</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>83.5</v>
+      </c>
+      <c r="I14">
+        <v>1622.8</v>
+      </c>
+      <c r="J14">
+        <v>86.8</v>
+      </c>
+      <c r="K14">
+        <v>1174.5</v>
+      </c>
+      <c r="L14">
+        <v>68.5</v>
+      </c>
+      <c r="M14">
+        <v>1196.9000000000001</v>
+      </c>
+      <c r="N14">
+        <v>77.8</v>
+      </c>
+      <c r="O14">
+        <v>1076.4000000000001</v>
+      </c>
+      <c r="P14">
+        <v>1706.2</v>
+      </c>
+      <c r="Q14">
+        <v>1261.3</v>
+      </c>
+      <c r="R14">
+        <v>1265.4000000000001</v>
+      </c>
+      <c r="S14">
+        <v>1154.2</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>4</v>
+      </c>
+      <c r="Y14">
+        <v>1346.8</v>
+      </c>
+      <c r="Z14">
+        <v>212.3</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="AC14" s="4"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>37199</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C15">
+        <v>258</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>258.33333299999998</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44819</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15">
+        <v>68.5</v>
+      </c>
+      <c r="I15">
+        <v>233.7</v>
+      </c>
+      <c r="J15">
+        <v>58.9</v>
+      </c>
+      <c r="K15">
+        <v>217.8</v>
+      </c>
+      <c r="L15">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="M15">
+        <v>121.5</v>
+      </c>
+      <c r="N15">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="O15">
+        <v>590.70000000000005</v>
+      </c>
+      <c r="P15">
+        <v>302.10000000000002</v>
+      </c>
+      <c r="Q15">
+        <v>276.7</v>
+      </c>
+      <c r="R15">
+        <v>187.2</v>
+      </c>
+      <c r="S15">
+        <v>662.8</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>3</v>
+      </c>
+      <c r="Y15">
+        <v>255.3</v>
+      </c>
+      <c r="Z15">
+        <v>49.3</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="AC15" s="4"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>37564</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C16">
+        <v>258</v>
+      </c>
+      <c r="D16">
+        <v>13</v>
+      </c>
+      <c r="E16">
+        <v>258.54166700000002</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44819</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16">
+        <v>51.7</v>
+      </c>
+      <c r="I16">
+        <v>-3.6</v>
+      </c>
+      <c r="J16">
+        <v>63.7</v>
+      </c>
+      <c r="K16">
+        <v>208.5</v>
+      </c>
+      <c r="L16">
+        <v>80.5</v>
+      </c>
+      <c r="M16">
+        <v>63.4</v>
+      </c>
+      <c r="N16">
+        <v>74.2</v>
+      </c>
+      <c r="O16">
+        <v>94.8</v>
+      </c>
+      <c r="P16">
+        <v>48</v>
+      </c>
+      <c r="Q16">
+        <v>272.2</v>
+      </c>
+      <c r="R16">
+        <v>143.9</v>
+      </c>
+      <c r="S16">
+        <v>169</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>3</v>
+      </c>
+      <c r="Y16">
+        <v>195</v>
+      </c>
+      <c r="Z16">
+        <v>55.5</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AC16" s="4"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>37929</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C17">
+        <v>258</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>258.83333299999998</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44819</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17">
+        <v>57.7</v>
+      </c>
+      <c r="I17">
+        <v>135.6</v>
+      </c>
+      <c r="J17">
+        <v>66.2</v>
+      </c>
+      <c r="K17">
+        <v>471.8</v>
+      </c>
+      <c r="L17">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="M17">
+        <v>97.6</v>
+      </c>
+      <c r="N17">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="O17">
+        <v>-0.5</v>
+      </c>
+      <c r="P17">
+        <v>193.3</v>
+      </c>
+      <c r="Q17">
+        <v>538</v>
+      </c>
+      <c r="R17">
+        <v>168.1</v>
+      </c>
+      <c r="S17">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>3</v>
+      </c>
+      <c r="Y17">
+        <v>142.4</v>
+      </c>
+      <c r="Z17">
+        <v>55.1</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="AC17" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F607CB-9C39-994D-822C-D17B1ED40676}">
   <dimension ref="A1:AF17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11613,61 +13347,61 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>37196</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="C2">
+        <v>186</v>
+      </c>
+      <c r="D2">
         <v>11</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2">
         <v>186.45833300000001</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="1">
         <v>44747</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2">
         <v>237.7</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2">
         <v>298.2</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2">
         <v>300.8</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2">
         <v>242.1</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2">
         <v>305.10000000000002</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2">
         <v>535.9</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2">
         <v>300.8</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2">
         <v>547.20000000000005</v>
       </c>
       <c r="T2" s="7">
@@ -11719,59 +13453,61 @@
       </c>
     </row>
     <row r="3" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="1">
         <v>37561</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="7">
+      <c r="C3">
+        <v>186</v>
+      </c>
+      <c r="D3">
         <v>14</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3">
         <v>186.58333300000001</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="1">
         <v>44747</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3">
         <v>181.6</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3">
         <v>245.1</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3">
         <v>143.5</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3">
         <v>573</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3">
         <v>141.1</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3">
         <v>354.8</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3">
         <v>112.8</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3">
         <v>355.8</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3">
         <v>426.7</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3">
         <v>716.5</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3">
         <v>495.8</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3">
         <v>468.6</v>
       </c>
       <c r="T3" s="7">
@@ -11823,59 +13559,61 @@
       </c>
     </row>
     <row r="4" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="A4" s="1">
         <v>37926</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="7">
+      <c r="C4">
+        <v>186</v>
+      </c>
+      <c r="D4">
         <v>17</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <v>186.70833300000001</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="1">
         <v>44747</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <v>140.69999999999999</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4">
         <v>335.6</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4">
         <v>185.6</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4">
         <v>924.5</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4">
         <v>121.6</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4">
         <v>381.6</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4">
         <v>125.5</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4">
         <v>914.6</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4">
         <v>476.3</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4">
         <v>1110</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4">
         <v>503.1</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4">
         <v>1040.0999999999999</v>
       </c>
       <c r="T4" s="7">
@@ -11927,59 +13665,61 @@
       </c>
     </row>
     <row r="5" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="A5" s="1">
         <v>38292</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="2">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="7">
+      <c r="C5">
+        <v>186</v>
+      </c>
+      <c r="D5">
         <v>20</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>186.83333300000001</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="1">
         <v>44747</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5">
         <v>114.8</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
         <v>961.9</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5">
         <v>118.4</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5">
         <v>804.3</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5">
         <v>112.3</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5">
         <v>851.1</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5">
         <v>118.7</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5">
         <v>828.9</v>
       </c>
-      <c r="P5" s="7">
+      <c r="P5">
         <v>1076.8</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5">
         <v>922.7</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5">
         <v>963.4</v>
       </c>
-      <c r="S5" s="7">
+      <c r="S5">
         <v>947.6</v>
       </c>
       <c r="T5" s="7">
@@ -12031,60 +13771,62 @@
       </c>
     </row>
     <row r="6" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="A6" s="1">
         <v>38657</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="2">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="7">
+      <c r="C6">
+        <v>186</v>
+      </c>
+      <c r="D6">
         <v>23</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <v>186.95833300000001</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="1">
         <v>44747</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="7">
-        <v>114.8</v>
-      </c>
-      <c r="I6" s="7">
-        <v>961.9</v>
-      </c>
-      <c r="J6" s="7">
-        <v>118.4</v>
-      </c>
-      <c r="K6" s="7">
-        <v>804.3</v>
-      </c>
-      <c r="L6" s="7">
-        <v>112.3</v>
-      </c>
-      <c r="M6" s="7">
-        <v>851.1</v>
-      </c>
-      <c r="N6" s="7">
-        <v>118.7</v>
-      </c>
-      <c r="O6" s="7">
-        <v>828.9</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1076.8</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>922.7</v>
-      </c>
-      <c r="R6" s="7">
-        <v>963.4</v>
-      </c>
-      <c r="S6" s="7">
-        <v>947.6</v>
+      <c r="H6">
+        <v>124.2</v>
+      </c>
+      <c r="I6">
+        <v>305.60000000000002</v>
+      </c>
+      <c r="J6">
+        <v>118.2</v>
+      </c>
+      <c r="K6">
+        <v>474.6</v>
+      </c>
+      <c r="L6">
+        <v>94.8</v>
+      </c>
+      <c r="M6">
+        <v>559.6</v>
+      </c>
+      <c r="N6">
+        <v>110.5</v>
+      </c>
+      <c r="O6">
+        <v>337.3</v>
+      </c>
+      <c r="P6">
+        <v>429.9</v>
+      </c>
+      <c r="Q6">
+        <v>592.79999999999995</v>
+      </c>
+      <c r="R6">
+        <v>654.29999999999995</v>
+      </c>
+      <c r="S6">
+        <v>447.8</v>
       </c>
       <c r="T6" s="7">
         <v>1</v>
@@ -12103,92 +13845,98 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="5"/>
-        <v>880.63333333333333</v>
+        <v>400.83333333333331</v>
       </c>
       <c r="Z6" s="8">
         <f t="shared" si="6"/>
-        <v>71.248953208684625</v>
+        <v>138.40651477923043</v>
       </c>
       <c r="AA6" s="8">
         <f t="shared" si="0"/>
-        <v>115.26666666666667</v>
+        <v>109.83333333333333</v>
       </c>
       <c r="AB6" s="8">
         <f t="shared" si="1"/>
-        <v>54.006869752253309</v>
+        <v>37.961340601242881</v>
       </c>
       <c r="AC6" s="9">
         <f t="shared" si="2"/>
-        <v>0.1157412056096663</v>
+        <v>0.21507832898172324</v>
       </c>
       <c r="AD6" s="8">
         <f t="shared" si="3"/>
-        <v>995.9</v>
+        <v>510.66666666666663</v>
       </c>
       <c r="AE6" s="8">
         <f t="shared" si="4"/>
-        <v>70.419386535243277</v>
+        <v>124.80165597191942</v>
       </c>
       <c r="AF6" s="20">
         <f t="shared" si="7"/>
-        <v>7.0709294643280726E-2</v>
+        <v>0.24438966574135657</v>
       </c>
     </row>
     <row r="7" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="A7" s="1">
         <v>39022</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="7">
+      <c r="C7">
+        <v>187</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>187.08333300000001</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="1">
         <v>44748</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="7">
-        <v>124.2</v>
-      </c>
-      <c r="I7" s="7">
-        <v>305.60000000000002</v>
-      </c>
-      <c r="J7" s="7">
-        <v>118.2</v>
-      </c>
-      <c r="K7" s="7">
-        <v>474.6</v>
-      </c>
-      <c r="L7" s="7">
-        <v>94.8</v>
-      </c>
-      <c r="M7" s="7">
-        <v>559.6</v>
-      </c>
-      <c r="N7" s="7">
-        <v>110.5</v>
-      </c>
-      <c r="O7" s="7">
-        <v>337.3</v>
-      </c>
-      <c r="P7" s="7">
-        <v>429.9</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>592.79999999999995</v>
-      </c>
-      <c r="R7" s="7">
-        <v>654.29999999999995</v>
-      </c>
-      <c r="S7" s="7">
-        <v>447.8</v>
+      <c r="H7" s="4">
+        <v>128.894277241759</v>
+      </c>
+      <c r="I7" s="4">
+        <v>201.03869994973999</v>
+      </c>
+      <c r="J7" s="4">
+        <v>98.082383338050704</v>
+      </c>
+      <c r="K7" s="4">
+        <v>282.28948157027298</v>
+      </c>
+      <c r="L7" s="4">
+        <v>129.08580316799001</v>
+      </c>
+      <c r="M7" s="4">
+        <v>229.849355489983</v>
+      </c>
+      <c r="N7" s="4">
+        <v>120.31048240360499</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <f>H7+I7</f>
+        <v>329.93297719149899</v>
+      </c>
+      <c r="Q7" s="4">
+        <f>J7+K7</f>
+        <v>380.37186490832369</v>
+      </c>
+      <c r="R7" s="4">
+        <f>L7+M7</f>
+        <v>358.93515865797303</v>
+      </c>
+      <c r="S7" s="4">
+        <f>M7+N7</f>
+        <v>350.15983789358802</v>
       </c>
       <c r="T7" s="7">
         <v>1</v>
@@ -12207,91 +13955,93 @@
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="5"/>
-        <v>419.27500000000003</v>
+        <v>178.29438425249901</v>
       </c>
       <c r="Z7" s="8">
         <f t="shared" si="6"/>
-        <v>118.87509901853571</v>
+        <v>123.53014028695534</v>
       </c>
       <c r="AA7" s="8">
         <f t="shared" si="0"/>
-        <v>111.925</v>
+        <v>119.09323653785117</v>
       </c>
       <c r="AB7" s="8">
         <f t="shared" si="1"/>
-        <v>15.039536844262681</v>
+        <v>15.466026056423813</v>
       </c>
       <c r="AC7" s="9">
         <f t="shared" si="2"/>
-        <v>0.21070218373493974</v>
+        <v>0.4004646737525383</v>
       </c>
       <c r="AD7" s="8">
         <f t="shared" si="3"/>
-        <v>531.20000000000005</v>
+        <v>297.38762079035018</v>
       </c>
       <c r="AE7" s="8">
         <f t="shared" si="4"/>
-        <v>109.86403718536228</v>
+        <v>119.84712116124469</v>
       </c>
       <c r="AF7" s="20">
         <f t="shared" si="7"/>
-        <v>0.206822359159191</v>
+        <v>0.40299969730661217</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="1">
         <v>39387</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="7">
+      <c r="C8">
+        <v>187</v>
+      </c>
+      <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>187.20833300000001</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="1">
         <v>44748</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8">
         <v>125.3</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8">
         <v>136.1</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8">
         <v>142</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8">
         <v>178.1</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8">
         <v>144.6</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8">
         <v>-5</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8">
         <v>126.5</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8">
         <v>117.7</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8">
         <v>261.39999999999998</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8">
         <v>320.10000000000002</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8">
         <v>139.5</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8">
         <v>244.2</v>
       </c>
       <c r="T8" s="7">
@@ -12343,59 +14093,61 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="A9" s="1">
         <v>39753</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="7">
+      <c r="C9">
+        <v>187</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>187.33333300000001</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="1">
         <v>44748</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9">
         <v>107.9</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
         <v>34.4</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9">
         <v>119.8</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9">
         <v>22.6</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9">
         <v>115</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <v>44.4</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <v>136</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9">
         <v>-6.4</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9">
         <v>142.30000000000001</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9">
         <v>142.4</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9">
         <v>159.30000000000001</v>
       </c>
-      <c r="S9" s="7">
+      <c r="S9">
         <v>129.6</v>
       </c>
       <c r="T9" s="7">
@@ -12447,61 +14199,61 @@
       </c>
     </row>
     <row r="10" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
+      <c r="A10" s="1">
         <v>37197</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10">
         <v>209</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10">
         <v>8</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10">
         <v>209.33333300000001</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="1">
         <v>44770</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10">
         <v>172.1</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10">
         <v>143.80000000000001</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10">
         <v>168.2</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10">
         <v>12.3</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10">
         <v>159.80000000000001</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10">
         <v>1800.9</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10">
         <v>212.3</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10">
         <v>104.2</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10">
         <v>315.89999999999998</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10">
         <v>180.6</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10">
         <v>1960.6</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10">
         <v>316.5</v>
       </c>
       <c r="T10" s="12">
@@ -12553,59 +14305,61 @@
       </c>
     </row>
     <row r="11" spans="1:32" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10">
+      <c r="A11" s="1">
         <v>37562</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="12">
+      <c r="C11">
+        <v>209</v>
+      </c>
+      <c r="D11">
         <v>13</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11">
         <v>209.54166699999999</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="1">
         <v>44770</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11">
         <v>188.2</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11">
         <v>218.3</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11">
         <v>246.8</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11">
         <v>719.6</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11">
         <v>200.5</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11">
         <v>894.7</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11">
         <v>268.3</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11">
         <v>541.1</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11">
         <v>406.5</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11">
         <v>966.4</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11">
         <v>1095.2</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11">
         <v>809.3</v>
       </c>
       <c r="T11" s="12">
@@ -12657,61 +14411,61 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="A12" s="1">
         <v>37198</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12">
         <v>236</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12">
         <v>8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12">
         <v>236.33333300000001</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="1">
         <v>44797</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12">
         <v>87.8</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12">
         <v>1032.5</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12">
         <v>83.4</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12">
         <v>-3.9</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12">
         <v>79.099999999999994</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12">
         <v>628.9</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12">
         <v>86.7</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12">
         <v>493.5</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12">
         <v>1120.3</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="Q12">
         <v>79.400000000000006</v>
       </c>
-      <c r="R12" s="24">
+      <c r="R12">
         <v>708</v>
       </c>
-      <c r="S12" s="24">
+      <c r="S12">
         <v>580.20000000000005</v>
       </c>
       <c r="T12" s="24">
@@ -12763,59 +14517,61 @@
       </c>
     </row>
     <row r="13" spans="1:32" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22">
+      <c r="A13" s="1">
         <v>37563</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="24">
+      <c r="C13">
+        <v>236</v>
+      </c>
+      <c r="D13">
         <v>13</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13">
         <v>236.54166699999999</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="1">
         <v>44797</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13">
         <v>87.2</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13">
         <v>1178.8</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13">
         <v>69.3</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13">
         <v>1085.5</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13">
         <v>110</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13">
         <v>953.4</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13">
         <v>76.400000000000006</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13">
         <v>1118.2</v>
       </c>
-      <c r="P13" s="24">
+      <c r="P13">
         <v>1266</v>
       </c>
-      <c r="Q13" s="24">
+      <c r="Q13">
         <v>1154.9000000000001</v>
       </c>
-      <c r="R13" s="24">
+      <c r="R13">
         <v>1063.4000000000001</v>
       </c>
-      <c r="S13" s="24">
+      <c r="S13">
         <v>1194.5999999999999</v>
       </c>
       <c r="T13" s="24">
@@ -12867,59 +14623,61 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="1">
         <v>37928</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="2">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="24">
+      <c r="C14">
+        <v>236</v>
+      </c>
+      <c r="D14">
         <v>20</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14">
         <v>236.83333300000001</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="1">
         <v>44797</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14">
         <v>83.5</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14">
         <v>1622.8</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14">
         <v>86.8</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14">
         <v>1174.5</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14">
         <v>68.5</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14">
         <v>1196.9000000000001</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14">
         <v>77.8</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14">
         <v>1076.4000000000001</v>
       </c>
-      <c r="P14" s="24">
+      <c r="P14">
         <v>1706.2</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="Q14">
         <v>1261.3</v>
       </c>
-      <c r="R14" s="24">
+      <c r="R14">
         <v>1265.4000000000001</v>
       </c>
-      <c r="S14" s="24">
+      <c r="S14">
         <v>1154.2</v>
       </c>
       <c r="T14" s="24">
@@ -12971,61 +14729,61 @@
       </c>
     </row>
     <row r="15" spans="1:32" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15">
+      <c r="A15" s="1">
         <v>37199</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15">
         <v>258</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15">
         <v>8</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15">
         <v>258.33333299999998</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="1">
         <v>44819</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15">
         <v>68.5</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15">
         <v>233.7</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15">
         <v>58.9</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15">
         <v>217.8</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15">
         <v>65.599999999999994</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15">
         <v>121.5</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15">
         <v>72.099999999999994</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15">
         <v>590.70000000000005</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15">
         <v>302.10000000000002</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15">
         <v>276.7</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R15">
         <v>187.2</v>
       </c>
-      <c r="S15" s="17">
+      <c r="S15">
         <v>662.8</v>
       </c>
       <c r="T15" s="17">
@@ -13077,59 +14835,61 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="15">
+      <c r="A16" s="1">
         <v>37564</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="17">
+      <c r="C16">
+        <v>258</v>
+      </c>
+      <c r="D16">
         <v>13</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16">
         <v>258.54166700000002</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="1">
         <v>44819</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16">
         <v>51.7</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16">
         <v>-3.6</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16">
         <v>63.7</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16">
         <v>208.5</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16">
         <v>80.5</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16">
         <v>63.4</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16">
         <v>74.2</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16">
         <v>94.8</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16">
         <v>48</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16">
         <v>272.2</v>
       </c>
-      <c r="R16" s="17">
+      <c r="R16">
         <v>143.9</v>
       </c>
-      <c r="S16" s="17">
+      <c r="S16">
         <v>169</v>
       </c>
       <c r="T16" s="17">
@@ -13181,59 +14941,61 @@
       </c>
     </row>
     <row r="17" spans="1:32" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15">
+      <c r="A17" s="1">
         <v>37929</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="2">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="17">
+      <c r="C17">
+        <v>258</v>
+      </c>
+      <c r="D17">
         <v>20</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17">
         <v>258.83333299999998</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="1">
         <v>44819</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17">
         <v>57.7</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17">
         <v>135.6</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17">
         <v>66.2</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17">
         <v>471.8</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17">
         <v>70.400000000000006</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17">
         <v>97.6</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17">
         <v>66.400000000000006</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17">
         <v>-0.5</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17">
         <v>193.3</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17">
         <v>538</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17">
         <v>168.1</v>
       </c>
-      <c r="S17" s="17">
+      <c r="S17">
         <v>65.900000000000006</v>
       </c>
       <c r="T17" s="17">
@@ -13282,6 +15044,2061 @@
       <c r="AF17" s="28">
         <f t="shared" si="7"/>
         <v>0.47365050345753623</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5968C-F606-6A41-9D9C-86DFC7E4FA78}">
+  <dimension ref="A1:AH18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>37196</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="7">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7">
+        <v>186.45833300000001</v>
+      </c>
+      <c r="F2" s="5">
+        <v>44747</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="40">
+        <f>glucose!H2*6/1000</f>
+        <v>1.4261999999999999</v>
+      </c>
+      <c r="I2" s="40">
+        <f>glucose!I2*6/1000</f>
+        <v>1.7891999999999999</v>
+      </c>
+      <c r="J2" s="40">
+        <f>glucose!J2*6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="40">
+        <f>glucose!K2*6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="40">
+        <f>glucose!L2*6/1000</f>
+        <v>1.8048000000000002</v>
+      </c>
+      <c r="M2" s="40">
+        <f>glucose!M2*6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="40">
+        <f>glucose!N2*6/1000</f>
+        <v>1.4525999999999999</v>
+      </c>
+      <c r="O2" s="40">
+        <f>glucose!O2*6/1000</f>
+        <v>1.8306000000000002</v>
+      </c>
+      <c r="P2" s="40">
+        <f>glucose!P2*6/1000</f>
+        <v>3.2153999999999998</v>
+      </c>
+      <c r="Q2" s="40">
+        <f>glucose!Q2*6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="40">
+        <f>glucose!R2*6/1000</f>
+        <v>1.8048000000000002</v>
+      </c>
+      <c r="S2" s="40">
+        <f>glucose!S2*6/1000</f>
+        <v>3.2832000000000003</v>
+      </c>
+      <c r="T2" s="7">
+        <v>1</v>
+      </c>
+      <c r="U2" s="7">
+        <v>0</v>
+      </c>
+      <c r="V2" s="7">
+        <v>0</v>
+      </c>
+      <c r="W2" s="7">
+        <v>1</v>
+      </c>
+      <c r="X2" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="8">
+        <f>(I2*T2+K2*U2+M2*V2+O2*W2)/X2</f>
+        <v>1.8099000000000001</v>
+      </c>
+      <c r="Z2" s="8">
+        <f>SQRT((((I2-$Y2)^2)*T2+((K2-$Y2)^2)*U2+((M2-$Y2)^2)*V2+((O2-$Y2)^2)*W2)/(X2-1))</f>
+        <v>2.9274220741123298E-2</v>
+      </c>
+      <c r="AA2" s="8">
+        <f t="shared" ref="AA2:AA17" si="0">(H2*T2+J2*U2+L2*V2+N2*W2)/X2</f>
+        <v>1.4394</v>
+      </c>
+      <c r="AB2" s="8">
+        <f t="shared" ref="AB2:AB17" si="1">SQRT((((H2-$Z2)^2)*T2+((J2-$Z2)^2)*U2+((L2-$Z2)^2)*V2+((N2-$Z2)^2)*W2)/(X2-1))</f>
+        <v>1.9943063723161765</v>
+      </c>
+      <c r="AC2" s="9">
+        <f t="shared" ref="AC2:AC17" si="2">AA2/(Y2+AA2)</f>
+        <v>0.44298772043209311</v>
+      </c>
+      <c r="AD2" s="8">
+        <f t="shared" ref="AD2:AD17" si="3">Y2+AA2</f>
+        <v>3.2492999999999999</v>
+      </c>
+      <c r="AE2" s="8">
+        <f>SQRT((((H2+I2-$AD2)^2)*T2+((J2+K2-$AD2)^2)*U2+((L2+M2-$AD2)^2)*V2+((N2+O2-$AD2)^2)*W2)/(X2-1))</f>
+        <v>4.7941839764447977E-2</v>
+      </c>
+      <c r="AF2" s="20">
+        <f>AE2/AD2</f>
+        <v>1.4754513207290178E-2</v>
+      </c>
+      <c r="AH2" s="8">
+        <f>((H2+I2-$AD$18)^2)*T2+((J2+K2-$AD$18)^2)*U2+((L2+M2-$AD$18)^2)*V2+((N2+O2-$AD$18)^2)*W2</f>
+        <v>0.16205401886897905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>37561</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="7">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7">
+        <v>186.58333300000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>44747</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="40">
+        <f>glucose!H3*6/1000</f>
+        <v>1.0895999999999999</v>
+      </c>
+      <c r="I3" s="40">
+        <f>glucose!I3*6/1000</f>
+        <v>1.4705999999999999</v>
+      </c>
+      <c r="J3" s="40">
+        <f>glucose!J3*6/1000</f>
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="K3" s="40">
+        <f>glucose!K3*6/1000</f>
+        <v>3.4380000000000002</v>
+      </c>
+      <c r="L3" s="40">
+        <f>glucose!L3*6/1000</f>
+        <v>0.84659999999999991</v>
+      </c>
+      <c r="M3" s="40">
+        <f>glucose!M3*6/1000</f>
+        <v>2.1288</v>
+      </c>
+      <c r="N3" s="40">
+        <f>glucose!N3*6/1000</f>
+        <v>0.67679999999999996</v>
+      </c>
+      <c r="O3" s="40">
+        <f>glucose!O3*6/1000</f>
+        <v>2.1348000000000003</v>
+      </c>
+      <c r="P3" s="40">
+        <f>glucose!P3*6/1000</f>
+        <v>2.5602</v>
+      </c>
+      <c r="Q3" s="40">
+        <f>glucose!Q3*6/1000</f>
+        <v>4.2990000000000004</v>
+      </c>
+      <c r="R3" s="40">
+        <f>glucose!R3*6/1000</f>
+        <v>2.9748000000000001</v>
+      </c>
+      <c r="S3" s="40">
+        <f>glucose!S3*6/1000</f>
+        <v>2.8116000000000003</v>
+      </c>
+      <c r="T3" s="7">
+        <v>1</v>
+      </c>
+      <c r="U3" s="7">
+        <v>1</v>
+      </c>
+      <c r="V3" s="7">
+        <v>1</v>
+      </c>
+      <c r="W3" s="7">
+        <v>1</v>
+      </c>
+      <c r="X3" s="7">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="8">
+        <f t="shared" ref="Y3:Y17" si="4">(I3*T3+K3*U3+M3*V3+O3*W3)/X3</f>
+        <v>2.29305</v>
+      </c>
+      <c r="Z3" s="8">
+        <f t="shared" ref="Z3:Z16" si="5">SQRT((((I3-$Y3)^2)*T3+((K3-$Y3)^2)*U3+((M3-$Y3)^2)*V3+((O3-$Y3)^2)*W3)/(X3-1))</f>
+        <v>0.82449087927035325</v>
+      </c>
+      <c r="AA3" s="8">
+        <f t="shared" si="0"/>
+        <v>0.86849999999999994</v>
+      </c>
+      <c r="AB3" s="8">
+        <f t="shared" si="1"/>
+        <v>0.17693423526797222</v>
+      </c>
+      <c r="AC3" s="9">
+        <f t="shared" si="2"/>
+        <v>0.27470702661669116</v>
+      </c>
+      <c r="AD3" s="8">
+        <f t="shared" si="3"/>
+        <v>3.1615500000000001</v>
+      </c>
+      <c r="AE3" s="8">
+        <f t="shared" ref="AE3:AE17" si="6">SQRT((((H3+I3-$AD3)^2)*T3+((J3+K3-$AD3)^2)*U3+((L3+M3-$AD3)^2)*V3+((N3+O3-$AD3)^2)*W3)/(X3-1))</f>
+        <v>0.77728826698979592</v>
+      </c>
+      <c r="AF3" s="20">
+        <f t="shared" ref="AF3:AF17" si="7">AE3/AD3</f>
+        <v>0.24585670541025634</v>
+      </c>
+      <c r="AH3" s="8">
+        <f t="shared" ref="AH3:AH17" si="8">((H3+I3-$AD$18)^2)*T3+((J3+K3-$AD$18)^2)*U3+((L3+M3-$AD$18)^2)*V3+((N3+O3-$AD$18)^2)*W3</f>
+        <v>2.3612464764110173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>37926</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C4" s="49"/>
+      <c r="D4" s="7">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7">
+        <v>186.70833300000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>44747</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="40">
+        <f>glucose!H4*6/1000</f>
+        <v>0.84419999999999995</v>
+      </c>
+      <c r="I4" s="40">
+        <f>glucose!I4*6/1000</f>
+        <v>2.0136000000000003</v>
+      </c>
+      <c r="J4" s="40">
+        <f>glucose!J4*6/1000</f>
+        <v>1.1135999999999999</v>
+      </c>
+      <c r="K4" s="40">
+        <f>glucose!K4*6/1000</f>
+        <v>5.5469999999999997</v>
+      </c>
+      <c r="L4" s="40">
+        <f>glucose!L4*6/1000</f>
+        <v>0.72959999999999992</v>
+      </c>
+      <c r="M4" s="40">
+        <f>glucose!M4*6/1000</f>
+        <v>2.2896000000000005</v>
+      </c>
+      <c r="N4" s="40">
+        <f>glucose!N4*6/1000</f>
+        <v>0.753</v>
+      </c>
+      <c r="O4" s="40">
+        <f>glucose!O4*6/1000</f>
+        <v>5.4876000000000005</v>
+      </c>
+      <c r="P4" s="40">
+        <f>glucose!P4*6/1000</f>
+        <v>2.8578000000000001</v>
+      </c>
+      <c r="Q4" s="40">
+        <f>glucose!Q4*6/1000</f>
+        <v>6.66</v>
+      </c>
+      <c r="R4" s="40">
+        <f>glucose!R4*6/1000</f>
+        <v>3.0186000000000002</v>
+      </c>
+      <c r="S4" s="40">
+        <f>glucose!S4*6/1000</f>
+        <v>6.2405999999999997</v>
+      </c>
+      <c r="T4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7">
+        <v>1</v>
+      </c>
+      <c r="V4" s="7">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7">
+        <v>1</v>
+      </c>
+      <c r="X4" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="8">
+        <f t="shared" si="4"/>
+        <v>5.5173000000000005</v>
+      </c>
+      <c r="Z4" s="8">
+        <f t="shared" si="5"/>
+        <v>4.200214280248038E-2</v>
+      </c>
+      <c r="AA4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.93330000000000002</v>
+      </c>
+      <c r="AB4" s="8">
+        <f t="shared" si="1"/>
+        <v>1.2860170762823409</v>
+      </c>
+      <c r="AC4" s="9">
+        <f t="shared" si="2"/>
+        <v>0.14468421542182122</v>
+      </c>
+      <c r="AD4" s="8">
+        <f t="shared" si="3"/>
+        <v>6.4506000000000006</v>
+      </c>
+      <c r="AE4" s="8">
+        <f t="shared" si="6"/>
+        <v>0.2969848480983493</v>
+      </c>
+      <c r="AF4" s="20">
+        <f t="shared" si="7"/>
+        <v>4.6039879716359602E-2</v>
+      </c>
+      <c r="AH4" s="8">
+        <f t="shared" si="8"/>
+        <v>17.125508740714761</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>38292</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="7">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7">
+        <v>186.83333300000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>44747</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="40">
+        <f>glucose!H5*6/1000</f>
+        <v>0.68879999999999997</v>
+      </c>
+      <c r="I5" s="40">
+        <f>glucose!I5*6/1000</f>
+        <v>5.7713999999999999</v>
+      </c>
+      <c r="J5" s="40">
+        <f>glucose!J5*6/1000</f>
+        <v>0.71040000000000014</v>
+      </c>
+      <c r="K5" s="40">
+        <f>glucose!K5*6/1000</f>
+        <v>4.8257999999999992</v>
+      </c>
+      <c r="L5" s="40">
+        <f>glucose!L5*6/1000</f>
+        <v>0.67379999999999995</v>
+      </c>
+      <c r="M5" s="40">
+        <f>glucose!M5*6/1000</f>
+        <v>5.1066000000000003</v>
+      </c>
+      <c r="N5" s="40">
+        <f>glucose!N5*6/1000</f>
+        <v>0.71220000000000006</v>
+      </c>
+      <c r="O5" s="40">
+        <f>glucose!O5*6/1000</f>
+        <v>4.9733999999999998</v>
+      </c>
+      <c r="P5" s="40">
+        <f>glucose!P5*6/1000</f>
+        <v>6.460799999999999</v>
+      </c>
+      <c r="Q5" s="40">
+        <f>glucose!Q5*6/1000</f>
+        <v>5.5362000000000009</v>
+      </c>
+      <c r="R5" s="40">
+        <f>glucose!R5*6/1000</f>
+        <v>5.7803999999999993</v>
+      </c>
+      <c r="S5" s="40">
+        <f>glucose!S5*6/1000</f>
+        <v>5.6856</v>
+      </c>
+      <c r="T5" s="7">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7">
+        <v>1</v>
+      </c>
+      <c r="W5" s="7">
+        <v>1</v>
+      </c>
+      <c r="X5" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="8">
+        <f t="shared" si="4"/>
+        <v>5.2838000000000003</v>
+      </c>
+      <c r="Z5" s="8">
+        <f t="shared" si="5"/>
+        <v>0.42749371925210777</v>
+      </c>
+      <c r="AA5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.6916000000000001</v>
+      </c>
+      <c r="AB5" s="8">
+        <f t="shared" si="1"/>
+        <v>0.3240412185135198</v>
+      </c>
+      <c r="AC5" s="9">
+        <f t="shared" si="2"/>
+        <v>0.1157412056096663</v>
+      </c>
+      <c r="AD5" s="8">
+        <f t="shared" si="3"/>
+        <v>5.9754000000000005</v>
+      </c>
+      <c r="AE5" s="8">
+        <f t="shared" si="6"/>
+        <v>0.42251631921145921</v>
+      </c>
+      <c r="AF5" s="20">
+        <f t="shared" si="7"/>
+        <v>7.0709294643280643E-2</v>
+      </c>
+      <c r="AH5" s="8">
+        <f t="shared" si="8"/>
+        <v>18.268726735221179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>38657</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C6" s="49"/>
+      <c r="D6" s="7">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7">
+        <v>186.95833300000001</v>
+      </c>
+      <c r="F6" s="5">
+        <v>44747</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="40">
+        <f>glucose!H6*6/1000</f>
+        <v>0.74520000000000008</v>
+      </c>
+      <c r="I6" s="40">
+        <f>glucose!I6*6/1000</f>
+        <v>1.8336000000000001</v>
+      </c>
+      <c r="J6" s="40">
+        <f>glucose!J6*6/1000</f>
+        <v>0.70920000000000005</v>
+      </c>
+      <c r="K6" s="40">
+        <f>glucose!K6*6/1000</f>
+        <v>2.8476000000000004</v>
+      </c>
+      <c r="L6" s="40">
+        <f>glucose!L6*6/1000</f>
+        <v>0.56879999999999997</v>
+      </c>
+      <c r="M6" s="40">
+        <f>glucose!M6*6/1000</f>
+        <v>3.3576000000000006</v>
+      </c>
+      <c r="N6" s="40">
+        <f>glucose!N6*6/1000</f>
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="O6" s="40">
+        <f>glucose!O6*6/1000</f>
+        <v>2.0238</v>
+      </c>
+      <c r="P6" s="40">
+        <f>glucose!P6*6/1000</f>
+        <v>2.5793999999999997</v>
+      </c>
+      <c r="Q6" s="40">
+        <f>glucose!Q6*6/1000</f>
+        <v>3.5567999999999995</v>
+      </c>
+      <c r="R6" s="40">
+        <f>glucose!R6*6/1000</f>
+        <v>3.9257999999999997</v>
+      </c>
+      <c r="S6" s="40">
+        <f>glucose!S6*6/1000</f>
+        <v>2.6868000000000003</v>
+      </c>
+      <c r="T6" s="7">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7">
+        <v>1</v>
+      </c>
+      <c r="W6" s="7">
+        <v>1</v>
+      </c>
+      <c r="X6" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="8">
+        <f t="shared" si="4"/>
+        <v>2.4049999999999998</v>
+      </c>
+      <c r="Z6" s="8">
+        <f t="shared" si="5"/>
+        <v>0.83043908867538285</v>
+      </c>
+      <c r="AA6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="AB6" s="8">
+        <f t="shared" si="1"/>
+        <v>0.22776804360745753</v>
+      </c>
+      <c r="AC6" s="9">
+        <f t="shared" si="2"/>
+        <v>0.21507832898172324</v>
+      </c>
+      <c r="AD6" s="8">
+        <f t="shared" si="3"/>
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="AE6" s="8">
+        <f t="shared" si="6"/>
+        <v>0.74880993583151689</v>
+      </c>
+      <c r="AF6" s="20">
+        <f t="shared" si="7"/>
+        <v>0.24438966574135668</v>
+      </c>
+      <c r="AH6" s="8">
+        <f t="shared" si="8"/>
+        <v>1.7782985708514851</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>39022</v>
+      </c>
+      <c r="B7" s="6">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>187.08333300000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>44748</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="40">
+        <f>glucose!H7*6/1000</f>
+        <v>0.77336566345055391</v>
+      </c>
+      <c r="I7" s="40">
+        <f>glucose!I7*6/1000</f>
+        <v>1.20623219969844</v>
+      </c>
+      <c r="J7" s="40">
+        <f>glucose!J7*6/1000</f>
+        <v>0.58849430002830427</v>
+      </c>
+      <c r="K7" s="40">
+        <f>glucose!K7*6/1000</f>
+        <v>1.6937368894216378</v>
+      </c>
+      <c r="L7" s="40">
+        <f>glucose!L7*6/1000</f>
+        <v>0.77451481900794006</v>
+      </c>
+      <c r="M7" s="40">
+        <f>glucose!M7*6/1000</f>
+        <v>1.3790961329398979</v>
+      </c>
+      <c r="N7" s="40">
+        <f>glucose!N7*6/1000</f>
+        <v>0.72186289442162999</v>
+      </c>
+      <c r="O7" s="40">
+        <f>glucose!O7*6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="40">
+        <f>glucose!P7*6/1000</f>
+        <v>1.9795978631489939</v>
+      </c>
+      <c r="Q7" s="40">
+        <f>glucose!Q7*6/1000</f>
+        <v>2.2822311894499423</v>
+      </c>
+      <c r="R7" s="40">
+        <f>glucose!R7*6/1000</f>
+        <v>2.1536109519478384</v>
+      </c>
+      <c r="S7" s="40">
+        <f>glucose!S7*6/1000</f>
+        <v>2.1009590273615282</v>
+      </c>
+      <c r="T7" s="7">
+        <v>1</v>
+      </c>
+      <c r="U7" s="7">
+        <v>1</v>
+      </c>
+      <c r="V7" s="7">
+        <v>1</v>
+      </c>
+      <c r="W7" s="7">
+        <v>1</v>
+      </c>
+      <c r="X7" s="7">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="8">
+        <f t="shared" si="4"/>
+        <v>1.069766305514994</v>
+      </c>
+      <c r="Z7" s="8">
+        <f t="shared" si="5"/>
+        <v>0.74118084172173204</v>
+      </c>
+      <c r="AA7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.71455941922710697</v>
+      </c>
+      <c r="AB7" s="8">
+        <f t="shared" si="1"/>
+        <v>9.2796156338542837E-2</v>
+      </c>
+      <c r="AC7" s="9">
+        <f t="shared" si="2"/>
+        <v>0.40046467375253836</v>
+      </c>
+      <c r="AD7" s="8">
+        <f t="shared" si="3"/>
+        <v>1.7843257247421009</v>
+      </c>
+      <c r="AE7" s="8">
+        <f t="shared" si="6"/>
+        <v>0.71908272696746822</v>
+      </c>
+      <c r="AF7" s="20">
+        <f t="shared" si="7"/>
+        <v>0.40299969730661228</v>
+      </c>
+      <c r="AH7" s="8">
+        <f t="shared" si="8"/>
+        <v>13.76767529047731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>39387</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="7">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>187.20833300000001</v>
+      </c>
+      <c r="F8" s="5">
+        <v>44748</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="40">
+        <f>glucose!H8*6/1000</f>
+        <v>0.75179999999999991</v>
+      </c>
+      <c r="I8" s="40">
+        <f>glucose!I8*6/1000</f>
+        <v>0.81659999999999988</v>
+      </c>
+      <c r="J8" s="40">
+        <f>glucose!J8*6/1000</f>
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="K8" s="40">
+        <f>glucose!K8*6/1000</f>
+        <v>1.0686</v>
+      </c>
+      <c r="L8" s="40">
+        <f>glucose!L8*6/1000</f>
+        <v>0.86759999999999993</v>
+      </c>
+      <c r="M8" s="40">
+        <f>glucose!M8*6/1000</f>
+        <v>-0.03</v>
+      </c>
+      <c r="N8" s="40">
+        <f>glucose!N8*6/1000</f>
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="O8" s="40">
+        <f>glucose!O8*6/1000</f>
+        <v>0.70620000000000005</v>
+      </c>
+      <c r="P8" s="40">
+        <f>glucose!P8*6/1000</f>
+        <v>1.5683999999999998</v>
+      </c>
+      <c r="Q8" s="40">
+        <f>glucose!Q8*6/1000</f>
+        <v>1.9206000000000001</v>
+      </c>
+      <c r="R8" s="40">
+        <f>glucose!R8*6/1000</f>
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="S8" s="40">
+        <f>glucose!S8*6/1000</f>
+        <v>1.4651999999999998</v>
+      </c>
+      <c r="T8" s="7">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7">
+        <v>1</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>1</v>
+      </c>
+      <c r="X8" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="8">
+        <f t="shared" si="4"/>
+        <v>0.8637999999999999</v>
+      </c>
+      <c r="Z8" s="8">
+        <f t="shared" si="5"/>
+        <v>0.18575338489513452</v>
+      </c>
+      <c r="AA8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.78759999999999997</v>
+      </c>
+      <c r="AB8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.73922425702203265</v>
+      </c>
+      <c r="AC8" s="9">
+        <f t="shared" si="2"/>
+        <v>0.47692866658592714</v>
+      </c>
+      <c r="AD8" s="8">
+        <f t="shared" si="3"/>
+        <v>1.6513999999999998</v>
+      </c>
+      <c r="AE8" s="8">
+        <f t="shared" si="6"/>
+        <v>0.23877612946021209</v>
+      </c>
+      <c r="AF8" s="20">
+        <f t="shared" si="7"/>
+        <v>0.14459012320468217</v>
+      </c>
+      <c r="AH8" s="8">
+        <f t="shared" si="8"/>
+        <v>10.723169047890494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>39753</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="7">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>187.33333300000001</v>
+      </c>
+      <c r="F9" s="5">
+        <v>44748</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="40">
+        <f>glucose!H9*6/1000</f>
+        <v>0.64740000000000009</v>
+      </c>
+      <c r="I9" s="40">
+        <f>glucose!I9*6/1000</f>
+        <v>0.20639999999999997</v>
+      </c>
+      <c r="J9" s="40">
+        <f>glucose!J9*6/1000</f>
+        <v>0.71879999999999999</v>
+      </c>
+      <c r="K9" s="40">
+        <f>glucose!K9*6/1000</f>
+        <v>0.13560000000000003</v>
+      </c>
+      <c r="L9" s="40">
+        <f>glucose!L9*6/1000</f>
+        <v>0.69</v>
+      </c>
+      <c r="M9" s="40">
+        <f>glucose!M9*6/1000</f>
+        <v>0.26639999999999997</v>
+      </c>
+      <c r="N9" s="40">
+        <f>glucose!N9*6/1000</f>
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="O9" s="40">
+        <f>glucose!O9*6/1000</f>
+        <v>-3.8400000000000004E-2</v>
+      </c>
+      <c r="P9" s="40">
+        <f>glucose!P9*6/1000</f>
+        <v>0.85380000000000011</v>
+      </c>
+      <c r="Q9" s="40">
+        <f>glucose!Q9*6/1000</f>
+        <v>0.85440000000000005</v>
+      </c>
+      <c r="R9" s="40">
+        <f>glucose!R9*6/1000</f>
+        <v>0.95580000000000009</v>
+      </c>
+      <c r="S9" s="40">
+        <f>glucose!S9*6/1000</f>
+        <v>0.77759999999999996</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7">
+        <v>1</v>
+      </c>
+      <c r="V9" s="7">
+        <v>1</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="8">
+        <f t="shared" si="4"/>
+        <v>0.20279999999999998</v>
+      </c>
+      <c r="Z9" s="8">
+        <f t="shared" si="5"/>
+        <v>6.5474269755377928E-2</v>
+      </c>
+      <c r="AA9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.68540000000000001</v>
+      </c>
+      <c r="AB9" s="8">
+        <f t="shared" si="1"/>
+        <v>0.76010014243452939</v>
+      </c>
+      <c r="AC9" s="9">
+        <f t="shared" si="2"/>
+        <v>0.77167304661112368</v>
+      </c>
+      <c r="AD9" s="8">
+        <f t="shared" si="3"/>
+        <v>0.88819999999999999</v>
+      </c>
+      <c r="AE9" s="8">
+        <f t="shared" si="6"/>
+        <v>5.9063694432366733E-2</v>
+      </c>
+      <c r="AF9" s="20">
+        <f t="shared" si="7"/>
+        <v>6.6498192335472564E-2</v>
+      </c>
+      <c r="AH9" s="8">
+        <f t="shared" si="8"/>
+        <v>20.974848170311681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <v>37197</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C10" s="50">
+        <v>209</v>
+      </c>
+      <c r="D10" s="12">
+        <v>8</v>
+      </c>
+      <c r="E10" s="12">
+        <v>209.33333300000001</v>
+      </c>
+      <c r="F10" s="10">
+        <v>44770</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="41">
+        <f>glucose!H10*6/1000</f>
+        <v>1.0326</v>
+      </c>
+      <c r="I10" s="41">
+        <f>glucose!I10*6/1000</f>
+        <v>0.86280000000000012</v>
+      </c>
+      <c r="J10" s="41">
+        <f>glucose!J10*6/1000</f>
+        <v>1.0091999999999999</v>
+      </c>
+      <c r="K10" s="41">
+        <f>glucose!K10*6/1000</f>
+        <v>7.3800000000000004E-2</v>
+      </c>
+      <c r="L10" s="41">
+        <f>glucose!L10*6/1000</f>
+        <v>0.9588000000000001</v>
+      </c>
+      <c r="M10" s="41">
+        <f>glucose!M10*6/1000</f>
+        <v>10.805400000000002</v>
+      </c>
+      <c r="N10" s="41">
+        <f>glucose!N10*6/1000</f>
+        <v>1.2738000000000003</v>
+      </c>
+      <c r="O10" s="41">
+        <f>glucose!O10*6/1000</f>
+        <v>0.62520000000000009</v>
+      </c>
+      <c r="P10" s="41">
+        <f>glucose!P10*6/1000</f>
+        <v>1.8954</v>
+      </c>
+      <c r="Q10" s="41">
+        <f>glucose!Q10*6/1000</f>
+        <v>1.0835999999999999</v>
+      </c>
+      <c r="R10" s="41">
+        <f>glucose!R10*6/1000</f>
+        <v>11.763599999999999</v>
+      </c>
+      <c r="S10" s="41">
+        <f>glucose!S10*6/1000</f>
+        <v>1.899</v>
+      </c>
+      <c r="T10" s="12">
+        <v>1</v>
+      </c>
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
+        <v>0</v>
+      </c>
+      <c r="W10" s="12">
+        <v>1</v>
+      </c>
+      <c r="X10" s="12">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="13">
+        <f t="shared" si="4"/>
+        <v>0.74400000000000011</v>
+      </c>
+      <c r="Z10" s="13">
+        <f t="shared" si="5"/>
+        <v>0.16800857120992371</v>
+      </c>
+      <c r="AA10" s="13">
+        <f t="shared" si="0"/>
+        <v>1.1532</v>
+      </c>
+      <c r="AB10" s="13">
+        <f t="shared" si="1"/>
+        <v>1.4036712659034039</v>
+      </c>
+      <c r="AC10" s="14">
+        <f t="shared" si="2"/>
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="AD10" s="13">
+        <f t="shared" si="3"/>
+        <v>1.8972000000000002</v>
+      </c>
+      <c r="AE10" s="13">
+        <f t="shared" si="6"/>
+        <v>2.5455844122719189E-3</v>
+      </c>
+      <c r="AF10" s="21">
+        <f t="shared" si="7"/>
+        <v>1.3417585980771234E-3</v>
+      </c>
+      <c r="AH10" s="8">
+        <f t="shared" si="8"/>
+        <v>5.3446686444749254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10">
+        <v>37562</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="12">
+        <v>13</v>
+      </c>
+      <c r="E11" s="12">
+        <v>209.54166699999999</v>
+      </c>
+      <c r="F11" s="10">
+        <v>44770</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="41">
+        <f>glucose!H11*6/1000</f>
+        <v>1.1291999999999998</v>
+      </c>
+      <c r="I11" s="41">
+        <f>glucose!I11*6/1000</f>
+        <v>1.3098000000000001</v>
+      </c>
+      <c r="J11" s="41">
+        <f>glucose!J11*6/1000</f>
+        <v>1.4808000000000001</v>
+      </c>
+      <c r="K11" s="41">
+        <f>glucose!K11*6/1000</f>
+        <v>4.3176000000000005</v>
+      </c>
+      <c r="L11" s="41">
+        <f>glucose!L11*6/1000</f>
+        <v>1.2030000000000001</v>
+      </c>
+      <c r="M11" s="41">
+        <f>glucose!M11*6/1000</f>
+        <v>5.3682000000000007</v>
+      </c>
+      <c r="N11" s="41">
+        <f>glucose!N11*6/1000</f>
+        <v>1.6098000000000001</v>
+      </c>
+      <c r="O11" s="41">
+        <f>glucose!O11*6/1000</f>
+        <v>3.2466000000000004</v>
+      </c>
+      <c r="P11" s="41">
+        <f>glucose!P11*6/1000</f>
+        <v>2.4390000000000001</v>
+      </c>
+      <c r="Q11" s="41">
+        <f>glucose!Q11*6/1000</f>
+        <v>5.7984</v>
+      </c>
+      <c r="R11" s="41">
+        <f>glucose!R11*6/1000</f>
+        <v>6.571200000000001</v>
+      </c>
+      <c r="S11" s="41">
+        <f>glucose!S11*6/1000</f>
+        <v>4.8557999999999995</v>
+      </c>
+      <c r="T11" s="12">
+        <v>1</v>
+      </c>
+      <c r="U11" s="12">
+        <v>1</v>
+      </c>
+      <c r="V11" s="12">
+        <v>1</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
+      <c r="X11" s="12">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="13">
+        <f t="shared" si="4"/>
+        <v>3.5605500000000005</v>
+      </c>
+      <c r="Z11" s="13">
+        <f t="shared" si="5"/>
+        <v>1.7325475837621318</v>
+      </c>
+      <c r="AA11" s="13">
+        <f t="shared" si="0"/>
+        <v>1.3556999999999999</v>
+      </c>
+      <c r="AB11" s="13">
+        <f t="shared" si="1"/>
+        <v>0.49088110086164716</v>
+      </c>
+      <c r="AC11" s="14">
+        <f t="shared" si="2"/>
+        <v>0.27575896262395111</v>
+      </c>
+      <c r="AD11" s="13">
+        <f t="shared" si="3"/>
+        <v>4.9162500000000007</v>
+      </c>
+      <c r="AE11" s="13">
+        <f t="shared" si="6"/>
+        <v>1.7941941282926999</v>
+      </c>
+      <c r="AF11" s="21">
+        <f t="shared" si="7"/>
+        <v>0.36495176776866506</v>
+      </c>
+      <c r="AH11" s="8">
+        <f t="shared" si="8"/>
+        <v>17.32280272680855</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="22">
+        <v>37198</v>
+      </c>
+      <c r="B12" s="23">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C12" s="53">
+        <v>236</v>
+      </c>
+      <c r="D12" s="24">
+        <v>8</v>
+      </c>
+      <c r="E12" s="24">
+        <v>236.33333300000001</v>
+      </c>
+      <c r="F12" s="22">
+        <v>44797</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="42">
+        <f>glucose!H12*6/1000</f>
+        <v>0.52679999999999993</v>
+      </c>
+      <c r="I12" s="42">
+        <f>glucose!I12*6/1000</f>
+        <v>6.1950000000000003</v>
+      </c>
+      <c r="J12" s="42">
+        <f>glucose!J12*6/1000</f>
+        <v>0.50040000000000007</v>
+      </c>
+      <c r="K12" s="42">
+        <f>glucose!K12*6/1000</f>
+        <v>-2.3399999999999997E-2</v>
+      </c>
+      <c r="L12" s="42">
+        <f>glucose!L12*6/1000</f>
+        <v>0.47459999999999997</v>
+      </c>
+      <c r="M12" s="42">
+        <f>glucose!M12*6/1000</f>
+        <v>3.7733999999999996</v>
+      </c>
+      <c r="N12" s="42">
+        <f>glucose!N12*6/1000</f>
+        <v>0.5202</v>
+      </c>
+      <c r="O12" s="42">
+        <f>glucose!O12*6/1000</f>
+        <v>2.9609999999999999</v>
+      </c>
+      <c r="P12" s="42">
+        <f>glucose!P12*6/1000</f>
+        <v>6.7217999999999991</v>
+      </c>
+      <c r="Q12" s="42">
+        <f>glucose!Q12*6/1000</f>
+        <v>0.47640000000000005</v>
+      </c>
+      <c r="R12" s="42">
+        <f>glucose!R12*6/1000</f>
+        <v>4.2480000000000002</v>
+      </c>
+      <c r="S12" s="42">
+        <f>glucose!S12*6/1000</f>
+        <v>3.4812000000000003</v>
+      </c>
+      <c r="T12" s="24">
+        <v>1</v>
+      </c>
+      <c r="U12" s="24">
+        <v>0</v>
+      </c>
+      <c r="V12" s="24">
+        <v>1</v>
+      </c>
+      <c r="W12" s="24">
+        <v>1</v>
+      </c>
+      <c r="X12" s="24">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="25">
+        <f t="shared" si="4"/>
+        <v>4.3098000000000001</v>
+      </c>
+      <c r="Z12" s="25">
+        <f t="shared" si="5"/>
+        <v>1.6824038516361048</v>
+      </c>
+      <c r="AA12" s="25">
+        <f t="shared" si="0"/>
+        <v>0.50719999999999998</v>
+      </c>
+      <c r="AB12" s="25">
+        <f t="shared" si="1"/>
+        <v>1.4396055360238456</v>
+      </c>
+      <c r="AC12" s="26">
+        <f t="shared" si="2"/>
+        <v>0.10529375129748805</v>
+      </c>
+      <c r="AD12" s="25">
+        <f t="shared" si="3"/>
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AE12" s="25">
+        <f t="shared" si="6"/>
+        <v>1.6935739842120865</v>
+      </c>
+      <c r="AF12" s="27">
+        <f t="shared" si="7"/>
+        <v>0.35158272456136319</v>
+      </c>
+      <c r="AH12" s="8">
+        <f t="shared" si="8"/>
+        <v>10.690626550049149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="22">
+        <v>37563</v>
+      </c>
+      <c r="B13" s="23">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C13" s="53"/>
+      <c r="D13" s="24">
+        <v>13</v>
+      </c>
+      <c r="E13" s="24">
+        <v>236.54166699999999</v>
+      </c>
+      <c r="F13" s="22">
+        <v>44797</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="42">
+        <f>glucose!H13*6/1000</f>
+        <v>0.5232</v>
+      </c>
+      <c r="I13" s="42">
+        <f>glucose!I13*6/1000</f>
+        <v>7.0727999999999991</v>
+      </c>
+      <c r="J13" s="42">
+        <f>glucose!J13*6/1000</f>
+        <v>0.41579999999999995</v>
+      </c>
+      <c r="K13" s="42">
+        <f>glucose!K13*6/1000</f>
+        <v>6.5129999999999999</v>
+      </c>
+      <c r="L13" s="42">
+        <f>glucose!L13*6/1000</f>
+        <v>0.66</v>
+      </c>
+      <c r="M13" s="42">
+        <f>glucose!M13*6/1000</f>
+        <v>5.7203999999999997</v>
+      </c>
+      <c r="N13" s="42">
+        <f>glucose!N13*6/1000</f>
+        <v>0.45840000000000003</v>
+      </c>
+      <c r="O13" s="42">
+        <f>glucose!O13*6/1000</f>
+        <v>6.7092000000000009</v>
+      </c>
+      <c r="P13" s="42">
+        <f>glucose!P13*6/1000</f>
+        <v>7.5960000000000001</v>
+      </c>
+      <c r="Q13" s="42">
+        <f>glucose!Q13*6/1000</f>
+        <v>6.9294000000000002</v>
+      </c>
+      <c r="R13" s="42">
+        <f>glucose!R13*6/1000</f>
+        <v>6.3804000000000007</v>
+      </c>
+      <c r="S13" s="42">
+        <f>glucose!S13*6/1000</f>
+        <v>7.1675999999999993</v>
+      </c>
+      <c r="T13" s="24">
+        <v>1</v>
+      </c>
+      <c r="U13" s="24">
+        <v>1</v>
+      </c>
+      <c r="V13" s="24">
+        <v>1</v>
+      </c>
+      <c r="W13" s="24">
+        <v>1</v>
+      </c>
+      <c r="X13" s="24">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="25">
+        <f t="shared" si="4"/>
+        <v>6.5038499999999999</v>
+      </c>
+      <c r="Z13" s="25">
+        <f t="shared" si="5"/>
+        <v>0.57147480259413008</v>
+      </c>
+      <c r="AA13" s="25">
+        <f t="shared" si="0"/>
+        <v>0.51434999999999997</v>
+      </c>
+      <c r="AB13" s="25">
+        <f t="shared" si="1"/>
+        <v>0.12541626992496274</v>
+      </c>
+      <c r="AC13" s="26">
+        <f t="shared" si="2"/>
+        <v>7.3288022569889713E-2</v>
+      </c>
+      <c r="AD13" s="25">
+        <f t="shared" si="3"/>
+        <v>7.0182000000000002</v>
+      </c>
+      <c r="AE13" s="25">
+        <f t="shared" si="6"/>
+        <v>0.50693668243677126</v>
+      </c>
+      <c r="AF13" s="27">
+        <f t="shared" si="7"/>
+        <v>7.2231723581085067E-2</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="8"/>
+        <v>49.387363060747703</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
+        <v>37928</v>
+      </c>
+      <c r="B14" s="23">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="24">
+        <v>20</v>
+      </c>
+      <c r="E14" s="24">
+        <v>236.83333300000001</v>
+      </c>
+      <c r="F14" s="22">
+        <v>44797</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="42">
+        <f>glucose!H14*6/1000</f>
+        <v>0.501</v>
+      </c>
+      <c r="I14" s="42">
+        <f>glucose!I14*6/1000</f>
+        <v>9.7367999999999988</v>
+      </c>
+      <c r="J14" s="42">
+        <f>glucose!J14*6/1000</f>
+        <v>0.52079999999999993</v>
+      </c>
+      <c r="K14" s="42">
+        <f>glucose!K14*6/1000</f>
+        <v>7.0469999999999997</v>
+      </c>
+      <c r="L14" s="42">
+        <f>glucose!L14*6/1000</f>
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="M14" s="42">
+        <f>glucose!M14*6/1000</f>
+        <v>7.1814000000000009</v>
+      </c>
+      <c r="N14" s="42">
+        <f>glucose!N14*6/1000</f>
+        <v>0.46679999999999994</v>
+      </c>
+      <c r="O14" s="42">
+        <f>glucose!O14*6/1000</f>
+        <v>6.4584000000000001</v>
+      </c>
+      <c r="P14" s="42">
+        <f>glucose!P14*6/1000</f>
+        <v>10.237200000000001</v>
+      </c>
+      <c r="Q14" s="42">
+        <f>glucose!Q14*6/1000</f>
+        <v>7.5677999999999992</v>
+      </c>
+      <c r="R14" s="42">
+        <f>glucose!R14*6/1000</f>
+        <v>7.5924000000000005</v>
+      </c>
+      <c r="S14" s="42">
+        <f>glucose!S14*6/1000</f>
+        <v>6.9252000000000011</v>
+      </c>
+      <c r="T14" s="24">
+        <v>1</v>
+      </c>
+      <c r="U14" s="24">
+        <v>1</v>
+      </c>
+      <c r="V14" s="24">
+        <v>1</v>
+      </c>
+      <c r="W14" s="24">
+        <v>1</v>
+      </c>
+      <c r="X14" s="24">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="25">
+        <f t="shared" si="4"/>
+        <v>7.6059000000000001</v>
+      </c>
+      <c r="Z14" s="25">
+        <f t="shared" si="5"/>
+        <v>1.454883789173554</v>
+      </c>
+      <c r="AA14" s="25">
+        <f t="shared" si="0"/>
+        <v>0.47489999999999993</v>
+      </c>
+      <c r="AB14" s="25">
+        <f t="shared" si="1"/>
+        <v>1.1326090452537489</v>
+      </c>
+      <c r="AC14" s="26">
+        <f t="shared" si="2"/>
+        <v>5.8768933768933759E-2</v>
+      </c>
+      <c r="AD14" s="25">
+        <f t="shared" si="3"/>
+        <v>8.0808</v>
+      </c>
+      <c r="AE14" s="25">
+        <f t="shared" si="6"/>
+        <v>1.4708006799019357</v>
+      </c>
+      <c r="AF14" s="27">
+        <f t="shared" si="7"/>
+        <v>0.18201176614963069</v>
+      </c>
+      <c r="AH14" s="8">
+        <f t="shared" si="8"/>
+        <v>89.258760473192211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>37199</v>
+      </c>
+      <c r="B15" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C15" s="52">
+        <v>258</v>
+      </c>
+      <c r="D15" s="17">
+        <v>8</v>
+      </c>
+      <c r="E15" s="17">
+        <v>258.33333299999998</v>
+      </c>
+      <c r="F15" s="15">
+        <v>44819</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="43">
+        <f>glucose!H15*6/1000</f>
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="I15" s="43">
+        <f>glucose!I15*6/1000</f>
+        <v>1.4021999999999999</v>
+      </c>
+      <c r="J15" s="43">
+        <f>glucose!J15*6/1000</f>
+        <v>0.35339999999999999</v>
+      </c>
+      <c r="K15" s="43">
+        <f>glucose!K15*6/1000</f>
+        <v>1.3068000000000002</v>
+      </c>
+      <c r="L15" s="43">
+        <f>glucose!L15*6/1000</f>
+        <v>0.39359999999999995</v>
+      </c>
+      <c r="M15" s="43">
+        <f>glucose!M15*6/1000</f>
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="N15" s="43">
+        <f>glucose!N15*6/1000</f>
+        <v>0.43259999999999998</v>
+      </c>
+      <c r="O15" s="43">
+        <f>glucose!O15*6/1000</f>
+        <v>3.5442000000000005</v>
+      </c>
+      <c r="P15" s="43">
+        <f>glucose!P15*6/1000</f>
+        <v>1.8126000000000002</v>
+      </c>
+      <c r="Q15" s="43">
+        <f>glucose!Q15*6/1000</f>
+        <v>1.6601999999999999</v>
+      </c>
+      <c r="R15" s="43">
+        <f>glucose!R15*6/1000</f>
+        <v>1.1231999999999998</v>
+      </c>
+      <c r="S15" s="43">
+        <f>glucose!S15*6/1000</f>
+        <v>3.9767999999999999</v>
+      </c>
+      <c r="T15" s="17">
+        <v>1</v>
+      </c>
+      <c r="U15" s="17">
+        <v>1</v>
+      </c>
+      <c r="V15" s="17">
+        <v>1</v>
+      </c>
+      <c r="W15" s="17">
+        <v>0</v>
+      </c>
+      <c r="X15" s="17">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="18">
+        <f t="shared" si="4"/>
+        <v>1.1460000000000001</v>
+      </c>
+      <c r="Z15" s="18">
+        <f t="shared" si="5"/>
+        <v>0.36426918617967124</v>
+      </c>
+      <c r="AA15" s="18">
+        <f t="shared" si="0"/>
+        <v>0.38599999999999995</v>
+      </c>
+      <c r="AB15" s="18">
+        <f t="shared" si="1"/>
+        <v>3.9763078401208879E-2</v>
+      </c>
+      <c r="AC15" s="19">
+        <f t="shared" si="2"/>
+        <v>0.25195822454308092</v>
+      </c>
+      <c r="AD15" s="18">
+        <f t="shared" si="3"/>
+        <v>1.532</v>
+      </c>
+      <c r="AE15" s="18">
+        <f t="shared" si="6"/>
+        <v>0.36270996677786521</v>
+      </c>
+      <c r="AF15" s="28">
+        <f t="shared" si="7"/>
+        <v>0.23675585298816268</v>
+      </c>
+      <c r="AH15" s="8">
+        <f t="shared" si="8"/>
+        <v>12.26223634971582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>37564</v>
+      </c>
+      <c r="B16" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="17">
+        <v>13</v>
+      </c>
+      <c r="E16" s="17">
+        <v>258.54166700000002</v>
+      </c>
+      <c r="F16" s="15">
+        <v>44819</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="43">
+        <f>glucose!H16*6/1000</f>
+        <v>0.31020000000000003</v>
+      </c>
+      <c r="I16" s="43">
+        <f>glucose!I16*6/1000</f>
+        <v>-2.1600000000000001E-2</v>
+      </c>
+      <c r="J16" s="43">
+        <f>glucose!J16*6/1000</f>
+        <v>0.38220000000000004</v>
+      </c>
+      <c r="K16" s="43">
+        <f>glucose!K16*6/1000</f>
+        <v>1.2509999999999999</v>
+      </c>
+      <c r="L16" s="43">
+        <f>glucose!L16*6/1000</f>
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="M16" s="43">
+        <f>glucose!M16*6/1000</f>
+        <v>0.38039999999999996</v>
+      </c>
+      <c r="N16" s="43">
+        <f>glucose!N16*6/1000</f>
+        <v>0.44520000000000004</v>
+      </c>
+      <c r="O16" s="43">
+        <f>glucose!O16*6/1000</f>
+        <v>0.56879999999999997</v>
+      </c>
+      <c r="P16" s="43">
+        <f>glucose!P16*6/1000</f>
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="Q16" s="43">
+        <f>glucose!Q16*6/1000</f>
+        <v>1.6331999999999998</v>
+      </c>
+      <c r="R16" s="43">
+        <f>glucose!R16*6/1000</f>
+        <v>0.86340000000000006</v>
+      </c>
+      <c r="S16" s="43">
+        <f>glucose!S16*6/1000</f>
+        <v>1.014</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>1</v>
+      </c>
+      <c r="V16" s="17">
+        <v>1</v>
+      </c>
+      <c r="W16" s="17">
+        <v>1</v>
+      </c>
+      <c r="X16" s="17">
+        <v>3</v>
+      </c>
+      <c r="Y16" s="18">
+        <f t="shared" si="4"/>
+        <v>0.73339999999999994</v>
+      </c>
+      <c r="Z16" s="18">
+        <f t="shared" si="5"/>
+        <v>0.45804580556970498</v>
+      </c>
+      <c r="AA16" s="18">
+        <f t="shared" si="0"/>
+        <v>0.43680000000000002</v>
+      </c>
+      <c r="AB16" s="18">
+        <f t="shared" si="1"/>
+        <v>5.7185281160964462E-2</v>
+      </c>
+      <c r="AC16" s="19">
+        <f t="shared" si="2"/>
+        <v>0.37326952657665363</v>
+      </c>
+      <c r="AD16" s="18">
+        <f t="shared" si="3"/>
+        <v>1.1701999999999999</v>
+      </c>
+      <c r="AE16" s="18">
+        <f t="shared" si="6"/>
+        <v>0.40797897004625128</v>
+      </c>
+      <c r="AF16" s="28">
+        <f t="shared" si="7"/>
+        <v>0.34864037775273571</v>
+      </c>
+      <c r="AH16" s="8">
+        <f t="shared" si="8"/>
+        <v>17.066151389920208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>37929</v>
+      </c>
+      <c r="B17" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="17">
+        <v>20</v>
+      </c>
+      <c r="E17" s="17">
+        <v>258.83333299999998</v>
+      </c>
+      <c r="F17" s="15">
+        <v>44819</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="43">
+        <f>glucose!H17*6/1000</f>
+        <v>0.34620000000000006</v>
+      </c>
+      <c r="I17" s="43">
+        <f>glucose!I17*6/1000</f>
+        <v>0.81359999999999988</v>
+      </c>
+      <c r="J17" s="43">
+        <f>glucose!J17*6/1000</f>
+        <v>0.39720000000000005</v>
+      </c>
+      <c r="K17" s="43">
+        <f>glucose!K17*6/1000</f>
+        <v>2.8308</v>
+      </c>
+      <c r="L17" s="43">
+        <f>glucose!L17*6/1000</f>
+        <v>0.42240000000000005</v>
+      </c>
+      <c r="M17" s="43">
+        <f>glucose!M17*6/1000</f>
+        <v>0.5855999999999999</v>
+      </c>
+      <c r="N17" s="43">
+        <f>glucose!N17*6/1000</f>
+        <v>0.39840000000000003</v>
+      </c>
+      <c r="O17" s="43">
+        <f>glucose!O17*6/1000</f>
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="P17" s="43">
+        <f>glucose!P17*6/1000</f>
+        <v>1.1598000000000002</v>
+      </c>
+      <c r="Q17" s="43">
+        <f>glucose!Q17*6/1000</f>
+        <v>3.2280000000000002</v>
+      </c>
+      <c r="R17" s="43">
+        <f>glucose!R17*6/1000</f>
+        <v>1.0085999999999999</v>
+      </c>
+      <c r="S17" s="43">
+        <f>glucose!S17*6/1000</f>
+        <v>0.39540000000000003</v>
+      </c>
+      <c r="T17" s="17">
+        <v>1</v>
+      </c>
+      <c r="U17" s="17">
+        <v>0</v>
+      </c>
+      <c r="V17" s="17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="17">
+        <v>1</v>
+      </c>
+      <c r="X17" s="17">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="18">
+        <f t="shared" si="4"/>
+        <v>0.46539999999999998</v>
+      </c>
+      <c r="Z17" s="18">
+        <f>SQRT((((I17-$Y17)^2)*T17+((K17-$Y17)^2)*U17+((M17-$Y17)^2)*V17+((O17-$Y17)^2)*W17)/(X17-1))</f>
+        <v>0.4213607955185199</v>
+      </c>
+      <c r="AA17" s="18">
+        <f t="shared" si="0"/>
+        <v>0.38900000000000007</v>
+      </c>
+      <c r="AB17" s="18">
+        <f t="shared" si="1"/>
+        <v>5.5576178618965709E-2</v>
+      </c>
+      <c r="AC17" s="19">
+        <f t="shared" si="2"/>
+        <v>0.45529026217228469</v>
+      </c>
+      <c r="AD17" s="18">
+        <f t="shared" si="3"/>
+        <v>0.85440000000000005</v>
+      </c>
+      <c r="AE17" s="18">
+        <f t="shared" si="6"/>
+        <v>0.40468699015411891</v>
+      </c>
+      <c r="AF17" s="28">
+        <f t="shared" si="7"/>
+        <v>0.47365050345753618</v>
+      </c>
+      <c r="AH17" s="8">
+        <f t="shared" si="8"/>
+        <v>21.834989326372785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AD18" s="18">
+        <f>AVERAGE(AD2:AD17)</f>
+        <v>3.5319266077963811</v>
+      </c>
+      <c r="AE18" s="18">
+        <f>AVERAGE(AE2:AE17)</f>
+        <v>0.62211817168685113</v>
+      </c>
+      <c r="AF18" s="3"/>
+      <c r="AH18" s="8">
+        <f>SQRT(SUM(AH2:AH17)/(SUM(X2:X17)-1))</f>
+        <v>2.5084718723005497</v>
       </c>
     </row>
   </sheetData>
@@ -13296,2064 +17113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5968C-F606-6A41-9D9C-86DFC7E4FA78}">
-  <dimension ref="A1:AH18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>37196</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="7">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7">
-        <v>186.45833300000001</v>
-      </c>
-      <c r="F2" s="5">
-        <v>44747</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="7">
-        <f>glucose!H2*6/1000</f>
-        <v>1.4261999999999999</v>
-      </c>
-      <c r="I2" s="7">
-        <f>glucose!I2*6/1000</f>
-        <v>1.7891999999999999</v>
-      </c>
-      <c r="J2" s="7">
-        <f>glucose!J2*6/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <f>glucose!K2*6/1000</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <f>glucose!L2*6/1000</f>
-        <v>1.8048000000000002</v>
-      </c>
-      <c r="M2" s="7">
-        <f>glucose!M2*6/1000</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <f>glucose!N2*6/1000</f>
-        <v>1.4525999999999999</v>
-      </c>
-      <c r="O2" s="7">
-        <f>glucose!O2*6/1000</f>
-        <v>1.8306000000000002</v>
-      </c>
-      <c r="P2" s="7">
-        <f>glucose!P2*6/1000</f>
-        <v>3.2153999999999998</v>
-      </c>
-      <c r="Q2" s="7">
-        <f>glucose!Q2*6/1000</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <f>glucose!R2*6/1000</f>
-        <v>1.8048000000000002</v>
-      </c>
-      <c r="S2" s="7">
-        <f>glucose!S2*6/1000</f>
-        <v>3.2832000000000003</v>
-      </c>
-      <c r="T2" s="7">
-        <v>1</v>
-      </c>
-      <c r="U2" s="7">
-        <v>0</v>
-      </c>
-      <c r="V2" s="7">
-        <v>0</v>
-      </c>
-      <c r="W2" s="7">
-        <v>1</v>
-      </c>
-      <c r="X2" s="7">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="8">
-        <f>(I2*T2+K2*U2+M2*V2+O2*W2)/X2</f>
-        <v>1.8099000000000001</v>
-      </c>
-      <c r="Z2" s="8">
-        <f>SQRT((((I2-$Y2)^2)*T2+((K2-$Y2)^2)*U2+((M2-$Y2)^2)*V2+((O2-$Y2)^2)*W2)/(X2-1))</f>
-        <v>2.9274220741123298E-2</v>
-      </c>
-      <c r="AA2" s="8">
-        <f t="shared" ref="AA2:AA17" si="0">(H2*T2+J2*U2+L2*V2+N2*W2)/X2</f>
-        <v>1.4394</v>
-      </c>
-      <c r="AB2" s="8">
-        <f t="shared" ref="AB2:AB17" si="1">SQRT((((H2-$Z2)^2)*T2+((J2-$Z2)^2)*U2+((L2-$Z2)^2)*V2+((N2-$Z2)^2)*W2)/(X2-1))</f>
-        <v>1.9943063723161765</v>
-      </c>
-      <c r="AC2" s="9">
-        <f t="shared" ref="AC2:AC17" si="2">AA2/(Y2+AA2)</f>
-        <v>0.44298772043209311</v>
-      </c>
-      <c r="AD2" s="8">
-        <f t="shared" ref="AD2:AD17" si="3">Y2+AA2</f>
-        <v>3.2492999999999999</v>
-      </c>
-      <c r="AE2" s="8">
-        <f>SQRT((((H2+I2-$AD2)^2)*T2+((J2+K2-$AD2)^2)*U2+((L2+M2-$AD2)^2)*V2+((N2+O2-$AD2)^2)*W2)/(X2-1))</f>
-        <v>4.7941839764447977E-2</v>
-      </c>
-      <c r="AF2" s="20">
-        <f>AE2/AD2</f>
-        <v>1.4754513207290178E-2</v>
-      </c>
-      <c r="AH2" s="8">
-        <f>((H2+I2-$AD$18)^2)*T2+((J2+K2-$AD$18)^2)*U2+((L2+M2-$AD$18)^2)*V2+((N2+O2-$AD$18)^2)*W2</f>
-        <v>0.61229996445312518</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>37561</v>
-      </c>
-      <c r="B3" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="7">
-        <v>14</v>
-      </c>
-      <c r="E3" s="7">
-        <v>186.58333300000001</v>
-      </c>
-      <c r="F3" s="5">
-        <v>44747</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="7">
-        <f>glucose!H3*6/1000</f>
-        <v>1.0895999999999999</v>
-      </c>
-      <c r="I3" s="7">
-        <f>glucose!I3*6/1000</f>
-        <v>1.4705999999999999</v>
-      </c>
-      <c r="J3" s="7">
-        <f>glucose!J3*6/1000</f>
-        <v>0.86099999999999999</v>
-      </c>
-      <c r="K3" s="7">
-        <f>glucose!K3*6/1000</f>
-        <v>3.4380000000000002</v>
-      </c>
-      <c r="L3" s="7">
-        <f>glucose!L3*6/1000</f>
-        <v>0.84659999999999991</v>
-      </c>
-      <c r="M3" s="7">
-        <f>glucose!M3*6/1000</f>
-        <v>2.1288</v>
-      </c>
-      <c r="N3" s="7">
-        <f>glucose!N3*6/1000</f>
-        <v>0.67679999999999996</v>
-      </c>
-      <c r="O3" s="7">
-        <f>glucose!O3*6/1000</f>
-        <v>2.1348000000000003</v>
-      </c>
-      <c r="P3" s="7">
-        <f>glucose!P3*6/1000</f>
-        <v>2.5602</v>
-      </c>
-      <c r="Q3" s="7">
-        <f>glucose!Q3*6/1000</f>
-        <v>4.2990000000000004</v>
-      </c>
-      <c r="R3" s="7">
-        <f>glucose!R3*6/1000</f>
-        <v>2.9748000000000001</v>
-      </c>
-      <c r="S3" s="7">
-        <f>glucose!S3*6/1000</f>
-        <v>2.8116000000000003</v>
-      </c>
-      <c r="T3" s="7">
-        <v>1</v>
-      </c>
-      <c r="U3" s="7">
-        <v>1</v>
-      </c>
-      <c r="V3" s="7">
-        <v>1</v>
-      </c>
-      <c r="W3" s="7">
-        <v>1</v>
-      </c>
-      <c r="X3" s="7">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="8">
-        <f t="shared" ref="Y3:Y17" si="4">(I3*T3+K3*U3+M3*V3+O3*W3)/X3</f>
-        <v>2.29305</v>
-      </c>
-      <c r="Z3" s="8">
-        <f t="shared" ref="Z3:Z16" si="5">SQRT((((I3-$Y3)^2)*T3+((K3-$Y3)^2)*U3+((M3-$Y3)^2)*V3+((O3-$Y3)^2)*W3)/(X3-1))</f>
-        <v>0.82449087927035325</v>
-      </c>
-      <c r="AA3" s="8">
-        <f t="shared" si="0"/>
-        <v>0.86849999999999994</v>
-      </c>
-      <c r="AB3" s="8">
-        <f t="shared" si="1"/>
-        <v>0.17693423526797222</v>
-      </c>
-      <c r="AC3" s="9">
-        <f t="shared" si="2"/>
-        <v>0.27470702661669116</v>
-      </c>
-      <c r="AD3" s="8">
-        <f t="shared" si="3"/>
-        <v>3.1615500000000001</v>
-      </c>
-      <c r="AE3" s="8">
-        <f t="shared" ref="AE3:AE17" si="6">SQRT((((H3+I3-$AD3)^2)*T3+((J3+K3-$AD3)^2)*U3+((L3+M3-$AD3)^2)*V3+((N3+O3-$AD3)^2)*W3)/(X3-1))</f>
-        <v>0.77728826698979592</v>
-      </c>
-      <c r="AF3" s="20">
-        <f t="shared" ref="AF3:AF17" si="7">AE3/AD3</f>
-        <v>0.24585670541025634</v>
-      </c>
-      <c r="AH3" s="8">
-        <f t="shared" ref="AH3:AH17" si="8">((H3+I3-$AD$18)^2)*T3+((J3+K3-$AD$18)^2)*U3+((L3+M3-$AD$18)^2)*V3+((N3+O3-$AD$18)^2)*W3</f>
-        <v>3.4510271514062492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>37926</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="7">
-        <v>17</v>
-      </c>
-      <c r="E4" s="7">
-        <v>186.70833300000001</v>
-      </c>
-      <c r="F4" s="5">
-        <v>44747</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="7">
-        <f>glucose!H4*6/1000</f>
-        <v>0.84419999999999995</v>
-      </c>
-      <c r="I4" s="7">
-        <f>glucose!I4*6/1000</f>
-        <v>2.0136000000000003</v>
-      </c>
-      <c r="J4" s="7">
-        <f>glucose!J4*6/1000</f>
-        <v>1.1135999999999999</v>
-      </c>
-      <c r="K4" s="7">
-        <f>glucose!K4*6/1000</f>
-        <v>5.5469999999999997</v>
-      </c>
-      <c r="L4" s="7">
-        <f>glucose!L4*6/1000</f>
-        <v>0.72959999999999992</v>
-      </c>
-      <c r="M4" s="7">
-        <f>glucose!M4*6/1000</f>
-        <v>2.2896000000000005</v>
-      </c>
-      <c r="N4" s="7">
-        <f>glucose!N4*6/1000</f>
-        <v>0.753</v>
-      </c>
-      <c r="O4" s="7">
-        <f>glucose!O4*6/1000</f>
-        <v>5.4876000000000005</v>
-      </c>
-      <c r="P4" s="7">
-        <f>glucose!P4*6/1000</f>
-        <v>2.8578000000000001</v>
-      </c>
-      <c r="Q4" s="7">
-        <f>glucose!Q4*6/1000</f>
-        <v>6.66</v>
-      </c>
-      <c r="R4" s="7">
-        <f>glucose!R4*6/1000</f>
-        <v>3.0186000000000002</v>
-      </c>
-      <c r="S4" s="7">
-        <f>glucose!S4*6/1000</f>
-        <v>6.2405999999999997</v>
-      </c>
-      <c r="T4" s="7">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7">
-        <v>1</v>
-      </c>
-      <c r="V4" s="7">
-        <v>0</v>
-      </c>
-      <c r="W4" s="7">
-        <v>1</v>
-      </c>
-      <c r="X4" s="7">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="8">
-        <f t="shared" si="4"/>
-        <v>5.5173000000000005</v>
-      </c>
-      <c r="Z4" s="8">
-        <f t="shared" si="5"/>
-        <v>4.200214280248038E-2</v>
-      </c>
-      <c r="AA4" s="8">
-        <f t="shared" si="0"/>
-        <v>0.93330000000000002</v>
-      </c>
-      <c r="AB4" s="8">
-        <f t="shared" si="1"/>
-        <v>1.2860170762823409</v>
-      </c>
-      <c r="AC4" s="9">
-        <f t="shared" si="2"/>
-        <v>0.14468421542182122</v>
-      </c>
-      <c r="AD4" s="8">
-        <f t="shared" si="3"/>
-        <v>6.4506000000000006</v>
-      </c>
-      <c r="AE4" s="8">
-        <f t="shared" si="6"/>
-        <v>0.2969848480983493</v>
-      </c>
-      <c r="AF4" s="20">
-        <f t="shared" si="7"/>
-        <v>4.6039879716359602E-2</v>
-      </c>
-      <c r="AH4" s="8">
-        <f t="shared" si="8"/>
-        <v>14.122933126953127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>38292</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="7">
-        <v>20</v>
-      </c>
-      <c r="E5" s="7">
-        <v>186.83333300000001</v>
-      </c>
-      <c r="F5" s="5">
-        <v>44747</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="7">
-        <f>glucose!H5*6/1000</f>
-        <v>0.68879999999999997</v>
-      </c>
-      <c r="I5" s="7">
-        <f>glucose!I5*6/1000</f>
-        <v>5.7713999999999999</v>
-      </c>
-      <c r="J5" s="7">
-        <f>glucose!J5*6/1000</f>
-        <v>0.71040000000000014</v>
-      </c>
-      <c r="K5" s="7">
-        <f>glucose!K5*6/1000</f>
-        <v>4.8257999999999992</v>
-      </c>
-      <c r="L5" s="7">
-        <f>glucose!L5*6/1000</f>
-        <v>0.67379999999999995</v>
-      </c>
-      <c r="M5" s="7">
-        <f>glucose!M5*6/1000</f>
-        <v>5.1066000000000003</v>
-      </c>
-      <c r="N5" s="7">
-        <f>glucose!N5*6/1000</f>
-        <v>0.71220000000000006</v>
-      </c>
-      <c r="O5" s="7">
-        <f>glucose!O5*6/1000</f>
-        <v>4.9733999999999998</v>
-      </c>
-      <c r="P5" s="7">
-        <f>glucose!P5*6/1000</f>
-        <v>6.460799999999999</v>
-      </c>
-      <c r="Q5" s="7">
-        <f>glucose!Q5*6/1000</f>
-        <v>5.5362000000000009</v>
-      </c>
-      <c r="R5" s="7">
-        <f>glucose!R5*6/1000</f>
-        <v>5.7803999999999993</v>
-      </c>
-      <c r="S5" s="7">
-        <f>glucose!S5*6/1000</f>
-        <v>5.6856</v>
-      </c>
-      <c r="T5" s="7">
-        <v>1</v>
-      </c>
-      <c r="U5" s="7">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7">
-        <v>1</v>
-      </c>
-      <c r="W5" s="7">
-        <v>1</v>
-      </c>
-      <c r="X5" s="7">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="8">
-        <f t="shared" si="4"/>
-        <v>5.2838000000000003</v>
-      </c>
-      <c r="Z5" s="8">
-        <f t="shared" si="5"/>
-        <v>0.42749371925210777</v>
-      </c>
-      <c r="AA5" s="8">
-        <f t="shared" si="0"/>
-        <v>0.6916000000000001</v>
-      </c>
-      <c r="AB5" s="8">
-        <f t="shared" si="1"/>
-        <v>0.3240412185135198</v>
-      </c>
-      <c r="AC5" s="9">
-        <f t="shared" si="2"/>
-        <v>0.1157412056096663</v>
-      </c>
-      <c r="AD5" s="8">
-        <f t="shared" si="3"/>
-        <v>5.9754000000000005</v>
-      </c>
-      <c r="AE5" s="8">
-        <f t="shared" si="6"/>
-        <v>0.42251631921145921</v>
-      </c>
-      <c r="AF5" s="20">
-        <f t="shared" si="7"/>
-        <v>7.0709294643280643E-2</v>
-      </c>
-      <c r="AH5" s="8">
-        <f t="shared" si="8"/>
-        <v>14.533666990429687</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>38657</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="7">
-        <v>23</v>
-      </c>
-      <c r="E6" s="7">
-        <v>186.95833300000001</v>
-      </c>
-      <c r="F6" s="5">
-        <v>44747</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="7">
-        <f>glucose!H6*6/1000</f>
-        <v>0.68879999999999997</v>
-      </c>
-      <c r="I6" s="7">
-        <f>glucose!I6*6/1000</f>
-        <v>5.7713999999999999</v>
-      </c>
-      <c r="J6" s="7">
-        <f>glucose!J6*6/1000</f>
-        <v>0.71040000000000014</v>
-      </c>
-      <c r="K6" s="7">
-        <f>glucose!K6*6/1000</f>
-        <v>4.8257999999999992</v>
-      </c>
-      <c r="L6" s="7">
-        <f>glucose!L6*6/1000</f>
-        <v>0.67379999999999995</v>
-      </c>
-      <c r="M6" s="7">
-        <f>glucose!M6*6/1000</f>
-        <v>5.1066000000000003</v>
-      </c>
-      <c r="N6" s="7">
-        <f>glucose!N6*6/1000</f>
-        <v>0.71220000000000006</v>
-      </c>
-      <c r="O6" s="7">
-        <f>glucose!O6*6/1000</f>
-        <v>4.9733999999999998</v>
-      </c>
-      <c r="P6" s="7">
-        <f>glucose!P6*6/1000</f>
-        <v>6.460799999999999</v>
-      </c>
-      <c r="Q6" s="7">
-        <f>glucose!Q6*6/1000</f>
-        <v>5.5362000000000009</v>
-      </c>
-      <c r="R6" s="7">
-        <f>glucose!R6*6/1000</f>
-        <v>5.7803999999999993</v>
-      </c>
-      <c r="S6" s="7">
-        <f>glucose!S6*6/1000</f>
-        <v>5.6856</v>
-      </c>
-      <c r="T6" s="7">
-        <v>1</v>
-      </c>
-      <c r="U6" s="7">
-        <v>0</v>
-      </c>
-      <c r="V6" s="7">
-        <v>1</v>
-      </c>
-      <c r="W6" s="7">
-        <v>1</v>
-      </c>
-      <c r="X6" s="7">
-        <v>3</v>
-      </c>
-      <c r="Y6" s="8">
-        <f t="shared" si="4"/>
-        <v>5.2838000000000003</v>
-      </c>
-      <c r="Z6" s="8">
-        <f t="shared" si="5"/>
-        <v>0.42749371925210777</v>
-      </c>
-      <c r="AA6" s="8">
-        <f t="shared" si="0"/>
-        <v>0.6916000000000001</v>
-      </c>
-      <c r="AB6" s="8">
-        <f t="shared" si="1"/>
-        <v>0.3240412185135198</v>
-      </c>
-      <c r="AC6" s="9">
-        <f t="shared" si="2"/>
-        <v>0.1157412056096663</v>
-      </c>
-      <c r="AD6" s="8">
-        <f t="shared" si="3"/>
-        <v>5.9754000000000005</v>
-      </c>
-      <c r="AE6" s="8">
-        <f t="shared" si="6"/>
-        <v>0.42251631921145921</v>
-      </c>
-      <c r="AF6" s="20">
-        <f t="shared" si="7"/>
-        <v>7.0709294643280643E-2</v>
-      </c>
-      <c r="AH6" s="8">
-        <f t="shared" si="8"/>
-        <v>14.533666990429687</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>39022</v>
-      </c>
-      <c r="B7" s="6">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="7">
-        <v>2</v>
-      </c>
-      <c r="E7" s="7">
-        <v>187.08333300000001</v>
-      </c>
-      <c r="F7" s="5">
-        <v>44748</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7">
-        <f>glucose!H7*6/1000</f>
-        <v>0.74520000000000008</v>
-      </c>
-      <c r="I7" s="7">
-        <f>glucose!I7*6/1000</f>
-        <v>1.8336000000000001</v>
-      </c>
-      <c r="J7" s="7">
-        <f>glucose!J7*6/1000</f>
-        <v>0.70920000000000005</v>
-      </c>
-      <c r="K7" s="7">
-        <f>glucose!K7*6/1000</f>
-        <v>2.8476000000000004</v>
-      </c>
-      <c r="L7" s="7">
-        <f>glucose!L7*6/1000</f>
-        <v>0.56879999999999997</v>
-      </c>
-      <c r="M7" s="7">
-        <f>glucose!M7*6/1000</f>
-        <v>3.3576000000000006</v>
-      </c>
-      <c r="N7" s="7">
-        <f>glucose!N7*6/1000</f>
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="O7" s="7">
-        <f>glucose!O7*6/1000</f>
-        <v>2.0238</v>
-      </c>
-      <c r="P7" s="7">
-        <f>glucose!P7*6/1000</f>
-        <v>2.5793999999999997</v>
-      </c>
-      <c r="Q7" s="7">
-        <f>glucose!Q7*6/1000</f>
-        <v>3.5567999999999995</v>
-      </c>
-      <c r="R7" s="7">
-        <f>glucose!R7*6/1000</f>
-        <v>3.9257999999999997</v>
-      </c>
-      <c r="S7" s="7">
-        <f>glucose!S7*6/1000</f>
-        <v>2.6868000000000003</v>
-      </c>
-      <c r="T7" s="7">
-        <v>1</v>
-      </c>
-      <c r="U7" s="7">
-        <v>1</v>
-      </c>
-      <c r="V7" s="7">
-        <v>1</v>
-      </c>
-      <c r="W7" s="7">
-        <v>1</v>
-      </c>
-      <c r="X7" s="7">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="8">
-        <f t="shared" si="4"/>
-        <v>2.5156500000000004</v>
-      </c>
-      <c r="Z7" s="8">
-        <f t="shared" si="5"/>
-        <v>0.71325059411121439</v>
-      </c>
-      <c r="AA7" s="8">
-        <f t="shared" si="0"/>
-        <v>0.67155000000000009</v>
-      </c>
-      <c r="AB7" s="8">
-        <f t="shared" si="1"/>
-        <v>9.023722106557619E-2</v>
-      </c>
-      <c r="AC7" s="9">
-        <f t="shared" si="2"/>
-        <v>0.21070218373493974</v>
-      </c>
-      <c r="AD7" s="8">
-        <f t="shared" si="3"/>
-        <v>3.1872000000000007</v>
-      </c>
-      <c r="AE7" s="8">
-        <f t="shared" si="6"/>
-        <v>0.65918422311217395</v>
-      </c>
-      <c r="AF7" s="20">
-        <f t="shared" si="7"/>
-        <v>0.20682235915919109</v>
-      </c>
-      <c r="AH7" s="8">
-        <f t="shared" si="8"/>
-        <v>2.8133673639062495</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>39387</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="7">
-        <v>5</v>
-      </c>
-      <c r="E8" s="7">
-        <v>187.20833300000001</v>
-      </c>
-      <c r="F8" s="5">
-        <v>44748</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="7">
-        <f>glucose!H8*6/1000</f>
-        <v>0.75179999999999991</v>
-      </c>
-      <c r="I8" s="7">
-        <f>glucose!I8*6/1000</f>
-        <v>0.81659999999999988</v>
-      </c>
-      <c r="J8" s="7">
-        <f>glucose!J8*6/1000</f>
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="K8" s="7">
-        <f>glucose!K8*6/1000</f>
-        <v>1.0686</v>
-      </c>
-      <c r="L8" s="7">
-        <f>glucose!L8*6/1000</f>
-        <v>0.86759999999999993</v>
-      </c>
-      <c r="M8" s="7">
-        <f>glucose!M8*6/1000</f>
-        <v>-0.03</v>
-      </c>
-      <c r="N8" s="7">
-        <f>glucose!N8*6/1000</f>
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="O8" s="7">
-        <f>glucose!O8*6/1000</f>
-        <v>0.70620000000000005</v>
-      </c>
-      <c r="P8" s="7">
-        <f>glucose!P8*6/1000</f>
-        <v>1.5683999999999998</v>
-      </c>
-      <c r="Q8" s="7">
-        <f>glucose!Q8*6/1000</f>
-        <v>1.9206000000000001</v>
-      </c>
-      <c r="R8" s="7">
-        <f>glucose!R8*6/1000</f>
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="S8" s="7">
-        <f>glucose!S8*6/1000</f>
-        <v>1.4651999999999998</v>
-      </c>
-      <c r="T8" s="7">
-        <v>1</v>
-      </c>
-      <c r="U8" s="7">
-        <v>1</v>
-      </c>
-      <c r="V8" s="7">
-        <v>0</v>
-      </c>
-      <c r="W8" s="7">
-        <v>1</v>
-      </c>
-      <c r="X8" s="7">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="8">
-        <f t="shared" si="4"/>
-        <v>0.8637999999999999</v>
-      </c>
-      <c r="Z8" s="8">
-        <f t="shared" si="5"/>
-        <v>0.18575338489513452</v>
-      </c>
-      <c r="AA8" s="8">
-        <f t="shared" si="0"/>
-        <v>0.78759999999999997</v>
-      </c>
-      <c r="AB8" s="8">
-        <f t="shared" si="1"/>
-        <v>0.73922425702203265</v>
-      </c>
-      <c r="AC8" s="9">
-        <f t="shared" si="2"/>
-        <v>0.47692866658592714</v>
-      </c>
-      <c r="AD8" s="8">
-        <f t="shared" si="3"/>
-        <v>1.6513999999999998</v>
-      </c>
-      <c r="AE8" s="8">
-        <f t="shared" si="6"/>
-        <v>0.23877612946021209</v>
-      </c>
-      <c r="AF8" s="20">
-        <f t="shared" si="7"/>
-        <v>0.14459012320468217</v>
-      </c>
-      <c r="AH8" s="8">
-        <f t="shared" si="8"/>
-        <v>13.983705040429689</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>39753</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="7">
-        <v>8</v>
-      </c>
-      <c r="E9" s="7">
-        <v>187.33333300000001</v>
-      </c>
-      <c r="F9" s="5">
-        <v>44748</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="7">
-        <f>glucose!H9*6/1000</f>
-        <v>0.64740000000000009</v>
-      </c>
-      <c r="I9" s="7">
-        <f>glucose!I9*6/1000</f>
-        <v>0.20639999999999997</v>
-      </c>
-      <c r="J9" s="7">
-        <f>glucose!J9*6/1000</f>
-        <v>0.71879999999999999</v>
-      </c>
-      <c r="K9" s="7">
-        <f>glucose!K9*6/1000</f>
-        <v>0.13560000000000003</v>
-      </c>
-      <c r="L9" s="7">
-        <f>glucose!L9*6/1000</f>
-        <v>0.69</v>
-      </c>
-      <c r="M9" s="7">
-        <f>glucose!M9*6/1000</f>
-        <v>0.26639999999999997</v>
-      </c>
-      <c r="N9" s="7">
-        <f>glucose!N9*6/1000</f>
-        <v>0.81599999999999995</v>
-      </c>
-      <c r="O9" s="7">
-        <f>glucose!O9*6/1000</f>
-        <v>-3.8400000000000004E-2</v>
-      </c>
-      <c r="P9" s="7">
-        <f>glucose!P9*6/1000</f>
-        <v>0.85380000000000011</v>
-      </c>
-      <c r="Q9" s="7">
-        <f>glucose!Q9*6/1000</f>
-        <v>0.85440000000000005</v>
-      </c>
-      <c r="R9" s="7">
-        <f>glucose!R9*6/1000</f>
-        <v>0.95580000000000009</v>
-      </c>
-      <c r="S9" s="7">
-        <f>glucose!S9*6/1000</f>
-        <v>0.77759999999999996</v>
-      </c>
-      <c r="T9" s="7">
-        <v>1</v>
-      </c>
-      <c r="U9" s="7">
-        <v>1</v>
-      </c>
-      <c r="V9" s="7">
-        <v>1</v>
-      </c>
-      <c r="W9" s="7">
-        <v>0</v>
-      </c>
-      <c r="X9" s="7">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="8">
-        <f t="shared" si="4"/>
-        <v>0.20279999999999998</v>
-      </c>
-      <c r="Z9" s="8">
-        <f t="shared" si="5"/>
-        <v>6.5474269755377928E-2</v>
-      </c>
-      <c r="AA9" s="8">
-        <f t="shared" si="0"/>
-        <v>0.68540000000000001</v>
-      </c>
-      <c r="AB9" s="8">
-        <f t="shared" si="1"/>
-        <v>0.76010014243452939</v>
-      </c>
-      <c r="AC9" s="9">
-        <f t="shared" si="2"/>
-        <v>0.77167304661112368</v>
-      </c>
-      <c r="AD9" s="8">
-        <f t="shared" si="3"/>
-        <v>0.88819999999999999</v>
-      </c>
-      <c r="AE9" s="8">
-        <f t="shared" si="6"/>
-        <v>5.9063694432366733E-2</v>
-      </c>
-      <c r="AF9" s="20">
-        <f t="shared" si="7"/>
-        <v>6.6498192335472564E-2</v>
-      </c>
-      <c r="AH9" s="8">
-        <f t="shared" si="8"/>
-        <v>25.470129460429689</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
-        <v>37197</v>
-      </c>
-      <c r="B10" s="11">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C10" s="30">
-        <v>209</v>
-      </c>
-      <c r="D10" s="12">
-        <v>8</v>
-      </c>
-      <c r="E10" s="12">
-        <v>209.33333300000001</v>
-      </c>
-      <c r="F10" s="10">
-        <v>44770</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="12">
-        <f>glucose!H10*6/1000</f>
-        <v>1.0326</v>
-      </c>
-      <c r="I10" s="12">
-        <f>glucose!I10*6/1000</f>
-        <v>0.86280000000000012</v>
-      </c>
-      <c r="J10" s="12">
-        <f>glucose!J10*6/1000</f>
-        <v>1.0091999999999999</v>
-      </c>
-      <c r="K10" s="12">
-        <f>glucose!K10*6/1000</f>
-        <v>7.3800000000000004E-2</v>
-      </c>
-      <c r="L10" s="12">
-        <f>glucose!L10*6/1000</f>
-        <v>0.9588000000000001</v>
-      </c>
-      <c r="M10" s="12">
-        <f>glucose!M10*6/1000</f>
-        <v>10.805400000000002</v>
-      </c>
-      <c r="N10" s="12">
-        <f>glucose!N10*6/1000</f>
-        <v>1.2738000000000003</v>
-      </c>
-      <c r="O10" s="12">
-        <f>glucose!O10*6/1000</f>
-        <v>0.62520000000000009</v>
-      </c>
-      <c r="P10" s="12">
-        <f>glucose!P10*6/1000</f>
-        <v>1.8954</v>
-      </c>
-      <c r="Q10" s="12">
-        <f>glucose!Q10*6/1000</f>
-        <v>1.0835999999999999</v>
-      </c>
-      <c r="R10" s="12">
-        <f>glucose!R10*6/1000</f>
-        <v>11.763599999999999</v>
-      </c>
-      <c r="S10" s="12">
-        <f>glucose!S10*6/1000</f>
-        <v>1.899</v>
-      </c>
-      <c r="T10" s="12">
-        <v>1</v>
-      </c>
-      <c r="U10" s="12">
-        <v>0</v>
-      </c>
-      <c r="V10" s="12">
-        <v>0</v>
-      </c>
-      <c r="W10" s="12">
-        <v>1</v>
-      </c>
-      <c r="X10" s="12">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="13">
-        <f t="shared" si="4"/>
-        <v>0.74400000000000011</v>
-      </c>
-      <c r="Z10" s="13">
-        <f t="shared" si="5"/>
-        <v>0.16800857120992371</v>
-      </c>
-      <c r="AA10" s="13">
-        <f t="shared" si="0"/>
-        <v>1.1532</v>
-      </c>
-      <c r="AB10" s="13">
-        <f t="shared" si="1"/>
-        <v>1.4036712659034039</v>
-      </c>
-      <c r="AC10" s="14">
-        <f t="shared" si="2"/>
-        <v>0.60784313725490191</v>
-      </c>
-      <c r="AD10" s="13">
-        <f t="shared" si="3"/>
-        <v>1.8972000000000002</v>
-      </c>
-      <c r="AE10" s="13">
-        <f t="shared" si="6"/>
-        <v>2.5455844122719189E-3</v>
-      </c>
-      <c r="AF10" s="21">
-        <f t="shared" si="7"/>
-        <v>1.3417585980771234E-3</v>
-      </c>
-      <c r="AH10" s="8">
-        <f t="shared" si="8"/>
-        <v>7.253247151953123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10">
-        <v>37562</v>
-      </c>
-      <c r="B11" s="11">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="12">
-        <v>13</v>
-      </c>
-      <c r="E11" s="12">
-        <v>209.54166699999999</v>
-      </c>
-      <c r="F11" s="10">
-        <v>44770</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="12">
-        <f>glucose!H11*6/1000</f>
-        <v>1.1291999999999998</v>
-      </c>
-      <c r="I11" s="12">
-        <f>glucose!I11*6/1000</f>
-        <v>1.3098000000000001</v>
-      </c>
-      <c r="J11" s="12">
-        <f>glucose!J11*6/1000</f>
-        <v>1.4808000000000001</v>
-      </c>
-      <c r="K11" s="12">
-        <f>glucose!K11*6/1000</f>
-        <v>4.3176000000000005</v>
-      </c>
-      <c r="L11" s="12">
-        <f>glucose!L11*6/1000</f>
-        <v>1.2030000000000001</v>
-      </c>
-      <c r="M11" s="12">
-        <f>glucose!M11*6/1000</f>
-        <v>5.3682000000000007</v>
-      </c>
-      <c r="N11" s="12">
-        <f>glucose!N11*6/1000</f>
-        <v>1.6098000000000001</v>
-      </c>
-      <c r="O11" s="12">
-        <f>glucose!O11*6/1000</f>
-        <v>3.2466000000000004</v>
-      </c>
-      <c r="P11" s="12">
-        <f>glucose!P11*6/1000</f>
-        <v>2.4390000000000001</v>
-      </c>
-      <c r="Q11" s="12">
-        <f>glucose!Q11*6/1000</f>
-        <v>5.7984</v>
-      </c>
-      <c r="R11" s="12">
-        <f>glucose!R11*6/1000</f>
-        <v>6.571200000000001</v>
-      </c>
-      <c r="S11" s="12">
-        <f>glucose!S11*6/1000</f>
-        <v>4.8557999999999995</v>
-      </c>
-      <c r="T11" s="12">
-        <v>1</v>
-      </c>
-      <c r="U11" s="12">
-        <v>1</v>
-      </c>
-      <c r="V11" s="12">
-        <v>1</v>
-      </c>
-      <c r="W11" s="12">
-        <v>1</v>
-      </c>
-      <c r="X11" s="12">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="13">
-        <f t="shared" si="4"/>
-        <v>3.5605500000000005</v>
-      </c>
-      <c r="Z11" s="13">
-        <f t="shared" si="5"/>
-        <v>1.7325475837621318</v>
-      </c>
-      <c r="AA11" s="13">
-        <f t="shared" si="0"/>
-        <v>1.3556999999999999</v>
-      </c>
-      <c r="AB11" s="13">
-        <f t="shared" si="1"/>
-        <v>0.49088110086164716</v>
-      </c>
-      <c r="AC11" s="14">
-        <f t="shared" si="2"/>
-        <v>0.27575896262395111</v>
-      </c>
-      <c r="AD11" s="13">
-        <f t="shared" si="3"/>
-        <v>4.9162500000000007</v>
-      </c>
-      <c r="AE11" s="13">
-        <f t="shared" si="6"/>
-        <v>1.7941941282926999</v>
-      </c>
-      <c r="AF11" s="21">
-        <f t="shared" si="7"/>
-        <v>0.36495176776866506</v>
-      </c>
-      <c r="AH11" s="8">
-        <f t="shared" si="8"/>
-        <v>14.627454866406261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
-        <v>37198</v>
-      </c>
-      <c r="B12" s="23">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C12" s="31">
-        <v>236</v>
-      </c>
-      <c r="D12" s="24">
-        <v>8</v>
-      </c>
-      <c r="E12" s="24">
-        <v>236.33333300000001</v>
-      </c>
-      <c r="F12" s="22">
-        <v>44797</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="24">
-        <f>glucose!H12*6/1000</f>
-        <v>0.52679999999999993</v>
-      </c>
-      <c r="I12" s="24">
-        <f>glucose!I12*6/1000</f>
-        <v>6.1950000000000003</v>
-      </c>
-      <c r="J12" s="24">
-        <f>glucose!J12*6/1000</f>
-        <v>0.50040000000000007</v>
-      </c>
-      <c r="K12" s="24">
-        <f>glucose!K12*6/1000</f>
-        <v>-2.3399999999999997E-2</v>
-      </c>
-      <c r="L12" s="24">
-        <f>glucose!L12*6/1000</f>
-        <v>0.47459999999999997</v>
-      </c>
-      <c r="M12" s="24">
-        <f>glucose!M12*6/1000</f>
-        <v>3.7733999999999996</v>
-      </c>
-      <c r="N12" s="24">
-        <f>glucose!N12*6/1000</f>
-        <v>0.5202</v>
-      </c>
-      <c r="O12" s="24">
-        <f>glucose!O12*6/1000</f>
-        <v>2.9609999999999999</v>
-      </c>
-      <c r="P12" s="24">
-        <f>glucose!P12*6/1000</f>
-        <v>6.7217999999999991</v>
-      </c>
-      <c r="Q12" s="24">
-        <f>glucose!Q12*6/1000</f>
-        <v>0.47640000000000005</v>
-      </c>
-      <c r="R12" s="24">
-        <f>glucose!R12*6/1000</f>
-        <v>4.2480000000000002</v>
-      </c>
-      <c r="S12" s="24">
-        <f>glucose!S12*6/1000</f>
-        <v>3.4812000000000003</v>
-      </c>
-      <c r="T12" s="24">
-        <v>1</v>
-      </c>
-      <c r="U12" s="24">
-        <v>0</v>
-      </c>
-      <c r="V12" s="24">
-        <v>1</v>
-      </c>
-      <c r="W12" s="24">
-        <v>1</v>
-      </c>
-      <c r="X12" s="24">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="25">
-        <f t="shared" si="4"/>
-        <v>4.3098000000000001</v>
-      </c>
-      <c r="Z12" s="25">
-        <f t="shared" si="5"/>
-        <v>1.6824038516361048</v>
-      </c>
-      <c r="AA12" s="25">
-        <f t="shared" si="0"/>
-        <v>0.50719999999999998</v>
-      </c>
-      <c r="AB12" s="25">
-        <f t="shared" si="1"/>
-        <v>1.4396055360238456</v>
-      </c>
-      <c r="AC12" s="26">
-        <f t="shared" si="2"/>
-        <v>0.10529375129748805</v>
-      </c>
-      <c r="AD12" s="25">
-        <f t="shared" si="3"/>
-        <v>4.8170000000000002</v>
-      </c>
-      <c r="AE12" s="25">
-        <f t="shared" si="6"/>
-        <v>1.6935739842120865</v>
-      </c>
-      <c r="AF12" s="27">
-        <f t="shared" si="7"/>
-        <v>0.35158272456136319</v>
-      </c>
-      <c r="AH12" s="8">
-        <f t="shared" si="8"/>
-        <v>8.8296875504296874</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22">
-        <v>37563</v>
-      </c>
-      <c r="B13" s="23">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="24">
-        <v>13</v>
-      </c>
-      <c r="E13" s="24">
-        <v>236.54166699999999</v>
-      </c>
-      <c r="F13" s="22">
-        <v>44797</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="24">
-        <f>glucose!H13*6/1000</f>
-        <v>0.5232</v>
-      </c>
-      <c r="I13" s="24">
-        <f>glucose!I13*6/1000</f>
-        <v>7.0727999999999991</v>
-      </c>
-      <c r="J13" s="24">
-        <f>glucose!J13*6/1000</f>
-        <v>0.41579999999999995</v>
-      </c>
-      <c r="K13" s="24">
-        <f>glucose!K13*6/1000</f>
-        <v>6.5129999999999999</v>
-      </c>
-      <c r="L13" s="24">
-        <f>glucose!L13*6/1000</f>
-        <v>0.66</v>
-      </c>
-      <c r="M13" s="24">
-        <f>glucose!M13*6/1000</f>
-        <v>5.7203999999999997</v>
-      </c>
-      <c r="N13" s="24">
-        <f>glucose!N13*6/1000</f>
-        <v>0.45840000000000003</v>
-      </c>
-      <c r="O13" s="24">
-        <f>glucose!O13*6/1000</f>
-        <v>6.7092000000000009</v>
-      </c>
-      <c r="P13" s="24">
-        <f>glucose!P13*6/1000</f>
-        <v>7.5960000000000001</v>
-      </c>
-      <c r="Q13" s="24">
-        <f>glucose!Q13*6/1000</f>
-        <v>6.9294000000000002</v>
-      </c>
-      <c r="R13" s="24">
-        <f>glucose!R13*6/1000</f>
-        <v>6.3804000000000007</v>
-      </c>
-      <c r="S13" s="24">
-        <f>glucose!S13*6/1000</f>
-        <v>7.1675999999999993</v>
-      </c>
-      <c r="T13" s="24">
-        <v>1</v>
-      </c>
-      <c r="U13" s="24">
-        <v>1</v>
-      </c>
-      <c r="V13" s="24">
-        <v>1</v>
-      </c>
-      <c r="W13" s="24">
-        <v>1</v>
-      </c>
-      <c r="X13" s="24">
-        <v>4</v>
-      </c>
-      <c r="Y13" s="25">
-        <f t="shared" si="4"/>
-        <v>6.5038499999999999</v>
-      </c>
-      <c r="Z13" s="25">
-        <f t="shared" si="5"/>
-        <v>0.57147480259413008</v>
-      </c>
-      <c r="AA13" s="25">
-        <f t="shared" si="0"/>
-        <v>0.51434999999999997</v>
-      </c>
-      <c r="AB13" s="25">
-        <f t="shared" si="1"/>
-        <v>0.12541626992496274</v>
-      </c>
-      <c r="AC13" s="26">
-        <f t="shared" si="2"/>
-        <v>7.3288022569889713E-2</v>
-      </c>
-      <c r="AD13" s="25">
-        <f t="shared" si="3"/>
-        <v>7.0182000000000002</v>
-      </c>
-      <c r="AE13" s="25">
-        <f t="shared" si="6"/>
-        <v>0.50693668243677126</v>
-      </c>
-      <c r="AF13" s="27">
-        <f t="shared" si="7"/>
-        <v>7.2231723581085067E-2</v>
-      </c>
-      <c r="AH13" s="8">
-        <f t="shared" si="8"/>
-        <v>42.157820793906254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
-        <v>37928</v>
-      </c>
-      <c r="B14" s="23">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="24">
-        <v>20</v>
-      </c>
-      <c r="E14" s="24">
-        <v>236.83333300000001</v>
-      </c>
-      <c r="F14" s="22">
-        <v>44797</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="24">
-        <f>glucose!H14*6/1000</f>
-        <v>0.501</v>
-      </c>
-      <c r="I14" s="24">
-        <f>glucose!I14*6/1000</f>
-        <v>9.7367999999999988</v>
-      </c>
-      <c r="J14" s="24">
-        <f>glucose!J14*6/1000</f>
-        <v>0.52079999999999993</v>
-      </c>
-      <c r="K14" s="24">
-        <f>glucose!K14*6/1000</f>
-        <v>7.0469999999999997</v>
-      </c>
-      <c r="L14" s="24">
-        <f>glucose!L14*6/1000</f>
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="M14" s="24">
-        <f>glucose!M14*6/1000</f>
-        <v>7.1814000000000009</v>
-      </c>
-      <c r="N14" s="24">
-        <f>glucose!N14*6/1000</f>
-        <v>0.46679999999999994</v>
-      </c>
-      <c r="O14" s="24">
-        <f>glucose!O14*6/1000</f>
-        <v>6.4584000000000001</v>
-      </c>
-      <c r="P14" s="24">
-        <f>glucose!P14*6/1000</f>
-        <v>10.237200000000001</v>
-      </c>
-      <c r="Q14" s="24">
-        <f>glucose!Q14*6/1000</f>
-        <v>7.5677999999999992</v>
-      </c>
-      <c r="R14" s="24">
-        <f>glucose!R14*6/1000</f>
-        <v>7.5924000000000005</v>
-      </c>
-      <c r="S14" s="24">
-        <f>glucose!S14*6/1000</f>
-        <v>6.9252000000000011</v>
-      </c>
-      <c r="T14" s="24">
-        <v>1</v>
-      </c>
-      <c r="U14" s="24">
-        <v>1</v>
-      </c>
-      <c r="V14" s="24">
-        <v>1</v>
-      </c>
-      <c r="W14" s="24">
-        <v>1</v>
-      </c>
-      <c r="X14" s="24">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="25">
-        <f t="shared" si="4"/>
-        <v>7.6059000000000001</v>
-      </c>
-      <c r="Z14" s="25">
-        <f t="shared" si="5"/>
-        <v>1.454883789173554</v>
-      </c>
-      <c r="AA14" s="25">
-        <f t="shared" si="0"/>
-        <v>0.47489999999999993</v>
-      </c>
-      <c r="AB14" s="25">
-        <f t="shared" si="1"/>
-        <v>1.1326090452537489</v>
-      </c>
-      <c r="AC14" s="26">
-        <f t="shared" si="2"/>
-        <v>5.8768933768933759E-2</v>
-      </c>
-      <c r="AD14" s="25">
-        <f t="shared" si="3"/>
-        <v>8.0808</v>
-      </c>
-      <c r="AE14" s="25">
-        <f t="shared" si="6"/>
-        <v>1.4708006799019357</v>
-      </c>
-      <c r="AF14" s="27">
-        <f t="shared" si="7"/>
-        <v>0.18201176614963069</v>
-      </c>
-      <c r="AH14" s="8">
-        <f t="shared" si="8"/>
-        <v>79.737044283906243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15">
-        <v>37199</v>
-      </c>
-      <c r="B15" s="16">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C15" s="32">
-        <v>258</v>
-      </c>
-      <c r="D15" s="17">
-        <v>8</v>
-      </c>
-      <c r="E15" s="17">
-        <v>258.33333299999998</v>
-      </c>
-      <c r="F15" s="15">
-        <v>44819</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="17">
-        <f>glucose!H15*6/1000</f>
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="I15" s="17">
-        <f>glucose!I15*6/1000</f>
-        <v>1.4021999999999999</v>
-      </c>
-      <c r="J15" s="17">
-        <f>glucose!J15*6/1000</f>
-        <v>0.35339999999999999</v>
-      </c>
-      <c r="K15" s="17">
-        <f>glucose!K15*6/1000</f>
-        <v>1.3068000000000002</v>
-      </c>
-      <c r="L15" s="17">
-        <f>glucose!L15*6/1000</f>
-        <v>0.39359999999999995</v>
-      </c>
-      <c r="M15" s="17">
-        <f>glucose!M15*6/1000</f>
-        <v>0.72899999999999998</v>
-      </c>
-      <c r="N15" s="17">
-        <f>glucose!N15*6/1000</f>
-        <v>0.43259999999999998</v>
-      </c>
-      <c r="O15" s="17">
-        <f>glucose!O15*6/1000</f>
-        <v>3.5442000000000005</v>
-      </c>
-      <c r="P15" s="17">
-        <f>glucose!P15*6/1000</f>
-        <v>1.8126000000000002</v>
-      </c>
-      <c r="Q15" s="17">
-        <f>glucose!Q15*6/1000</f>
-        <v>1.6601999999999999</v>
-      </c>
-      <c r="R15" s="17">
-        <f>glucose!R15*6/1000</f>
-        <v>1.1231999999999998</v>
-      </c>
-      <c r="S15" s="17">
-        <f>glucose!S15*6/1000</f>
-        <v>3.9767999999999999</v>
-      </c>
-      <c r="T15" s="17">
-        <v>1</v>
-      </c>
-      <c r="U15" s="17">
-        <v>1</v>
-      </c>
-      <c r="V15" s="17">
-        <v>1</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>3</v>
-      </c>
-      <c r="Y15" s="18">
-        <f t="shared" si="4"/>
-        <v>1.1460000000000001</v>
-      </c>
-      <c r="Z15" s="18">
-        <f t="shared" si="5"/>
-        <v>0.36426918617967124</v>
-      </c>
-      <c r="AA15" s="18">
-        <f t="shared" si="0"/>
-        <v>0.38599999999999995</v>
-      </c>
-      <c r="AB15" s="18">
-        <f t="shared" si="1"/>
-        <v>3.9763078401208879E-2</v>
-      </c>
-      <c r="AC15" s="19">
-        <f t="shared" si="2"/>
-        <v>0.25195822454308092</v>
-      </c>
-      <c r="AD15" s="18">
-        <f t="shared" si="3"/>
-        <v>1.532</v>
-      </c>
-      <c r="AE15" s="18">
-        <f t="shared" si="6"/>
-        <v>0.36270996677786521</v>
-      </c>
-      <c r="AF15" s="28">
-        <f t="shared" si="7"/>
-        <v>0.23675585298816268</v>
-      </c>
-      <c r="AH15" s="8">
-        <f t="shared" si="8"/>
-        <v>15.715943972929686</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="15">
-        <v>37564</v>
-      </c>
-      <c r="B16" s="16">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="17">
-        <v>13</v>
-      </c>
-      <c r="E16" s="17">
-        <v>258.54166700000002</v>
-      </c>
-      <c r="F16" s="15">
-        <v>44819</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="17">
-        <f>glucose!H16*6/1000</f>
-        <v>0.31020000000000003</v>
-      </c>
-      <c r="I16" s="17">
-        <f>glucose!I16*6/1000</f>
-        <v>-2.1600000000000001E-2</v>
-      </c>
-      <c r="J16" s="17">
-        <f>glucose!J16*6/1000</f>
-        <v>0.38220000000000004</v>
-      </c>
-      <c r="K16" s="17">
-        <f>glucose!K16*6/1000</f>
-        <v>1.2509999999999999</v>
-      </c>
-      <c r="L16" s="17">
-        <f>glucose!L16*6/1000</f>
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="M16" s="17">
-        <f>glucose!M16*6/1000</f>
-        <v>0.38039999999999996</v>
-      </c>
-      <c r="N16" s="17">
-        <f>glucose!N16*6/1000</f>
-        <v>0.44520000000000004</v>
-      </c>
-      <c r="O16" s="17">
-        <f>glucose!O16*6/1000</f>
-        <v>0.56879999999999997</v>
-      </c>
-      <c r="P16" s="17">
-        <f>glucose!P16*6/1000</f>
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="Q16" s="17">
-        <f>glucose!Q16*6/1000</f>
-        <v>1.6331999999999998</v>
-      </c>
-      <c r="R16" s="17">
-        <f>glucose!R16*6/1000</f>
-        <v>0.86340000000000006</v>
-      </c>
-      <c r="S16" s="17">
-        <f>glucose!S16*6/1000</f>
-        <v>1.014</v>
-      </c>
-      <c r="T16" s="17">
-        <v>0</v>
-      </c>
-      <c r="U16" s="17">
-        <v>1</v>
-      </c>
-      <c r="V16" s="17">
-        <v>1</v>
-      </c>
-      <c r="W16" s="17">
-        <v>1</v>
-      </c>
-      <c r="X16" s="17">
-        <v>3</v>
-      </c>
-      <c r="Y16" s="18">
-        <f t="shared" si="4"/>
-        <v>0.73339999999999994</v>
-      </c>
-      <c r="Z16" s="18">
-        <f t="shared" si="5"/>
-        <v>0.45804580556970498</v>
-      </c>
-      <c r="AA16" s="18">
-        <f t="shared" si="0"/>
-        <v>0.43680000000000002</v>
-      </c>
-      <c r="AB16" s="18">
-        <f t="shared" si="1"/>
-        <v>5.7185281160964462E-2</v>
-      </c>
-      <c r="AC16" s="19">
-        <f t="shared" si="2"/>
-        <v>0.37326952657665363</v>
-      </c>
-      <c r="AD16" s="18">
-        <f t="shared" si="3"/>
-        <v>1.1701999999999999</v>
-      </c>
-      <c r="AE16" s="18">
-        <f t="shared" si="6"/>
-        <v>0.40797897004625128</v>
-      </c>
-      <c r="AF16" s="28">
-        <f t="shared" si="7"/>
-        <v>0.34864037775273571</v>
-      </c>
-      <c r="AH16" s="8">
-        <f t="shared" si="8"/>
-        <v>21.105198175429688</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15">
-        <v>37929</v>
-      </c>
-      <c r="B17" s="16">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="17">
-        <v>20</v>
-      </c>
-      <c r="E17" s="17">
-        <v>258.83333299999998</v>
-      </c>
-      <c r="F17" s="15">
-        <v>44819</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="17">
-        <f>glucose!H17*6/1000</f>
-        <v>0.34620000000000006</v>
-      </c>
-      <c r="I17" s="17">
-        <f>glucose!I17*6/1000</f>
-        <v>0.81359999999999988</v>
-      </c>
-      <c r="J17" s="17">
-        <f>glucose!J17*6/1000</f>
-        <v>0.39720000000000005</v>
-      </c>
-      <c r="K17" s="17">
-        <f>glucose!K17*6/1000</f>
-        <v>2.8308</v>
-      </c>
-      <c r="L17" s="17">
-        <f>glucose!L17*6/1000</f>
-        <v>0.42240000000000005</v>
-      </c>
-      <c r="M17" s="17">
-        <f>glucose!M17*6/1000</f>
-        <v>0.5855999999999999</v>
-      </c>
-      <c r="N17" s="17">
-        <f>glucose!N17*6/1000</f>
-        <v>0.39840000000000003</v>
-      </c>
-      <c r="O17" s="17">
-        <f>glucose!O17*6/1000</f>
-        <v>-3.0000000000000001E-3</v>
-      </c>
-      <c r="P17" s="17">
-        <f>glucose!P17*6/1000</f>
-        <v>1.1598000000000002</v>
-      </c>
-      <c r="Q17" s="17">
-        <f>glucose!Q17*6/1000</f>
-        <v>3.2280000000000002</v>
-      </c>
-      <c r="R17" s="17">
-        <f>glucose!R17*6/1000</f>
-        <v>1.0085999999999999</v>
-      </c>
-      <c r="S17" s="17">
-        <f>glucose!S17*6/1000</f>
-        <v>0.39540000000000003</v>
-      </c>
-      <c r="T17" s="17">
-        <v>1</v>
-      </c>
-      <c r="U17" s="17">
-        <v>0</v>
-      </c>
-      <c r="V17" s="17">
-        <v>1</v>
-      </c>
-      <c r="W17" s="17">
-        <v>1</v>
-      </c>
-      <c r="X17" s="17">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="18">
-        <f t="shared" si="4"/>
-        <v>0.46539999999999998</v>
-      </c>
-      <c r="Z17" s="18">
-        <f>SQRT((((I17-$Y17)^2)*T17+((K17-$Y17)^2)*U17+((M17-$Y17)^2)*V17+((O17-$Y17)^2)*W17)/(X17-1))</f>
-        <v>0.4213607955185199</v>
-      </c>
-      <c r="AA17" s="18">
-        <f t="shared" si="0"/>
-        <v>0.38900000000000007</v>
-      </c>
-      <c r="AB17" s="18">
-        <f t="shared" si="1"/>
-        <v>5.5576178618965709E-2</v>
-      </c>
-      <c r="AC17" s="19">
-        <f t="shared" si="2"/>
-        <v>0.45529026217228469</v>
-      </c>
-      <c r="AD17" s="18">
-        <f t="shared" si="3"/>
-        <v>0.85440000000000005</v>
-      </c>
-      <c r="AE17" s="18">
-        <f t="shared" si="6"/>
-        <v>0.40468699015411891</v>
-      </c>
-      <c r="AF17" s="28">
-        <f t="shared" si="7"/>
-        <v>0.47365050345753618</v>
-      </c>
-      <c r="AH17" s="8">
-        <f t="shared" si="8"/>
-        <v>26.384954042929685</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="AD18" s="18">
-        <f>AVERAGE(AD2:AD17)</f>
-        <v>3.8015687499999999</v>
-      </c>
-      <c r="AF18" s="3"/>
-      <c r="AH18" s="8">
-        <f>SQRT(SUM(AH2:AH17)/(SUM(X2:X17)-1))</f>
-        <v>2.4962508496981912</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C2:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A70AB2F-7D05-F347-9806-82074D5EF7AF}">
   <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -15469,7 +17229,7 @@
       <c r="B2" s="6">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="7">
@@ -15559,9 +17319,9 @@
         <f>Y2/(Y2+AC2)</f>
         <v>0.557012279567907</v>
       </c>
-      <c r="AB2" s="33">
+      <c r="AB2" s="45">
         <f>AVERAGE(AA2:AA9)</f>
-        <v>0.68085434117225907</v>
+        <v>0.6447168894985521</v>
       </c>
       <c r="AC2" s="8">
         <f t="shared" ref="AC2:AC17" si="0">(H2*T2+J2*U2+L2*V2+N2*W2)/X2</f>
@@ -15575,12 +17335,12 @@
         <f>AC2/(Y2+AC2)</f>
         <v>0.44298772043209306</v>
       </c>
-      <c r="AF2" s="4">
-        <f>Y2+AC2</f>
+      <c r="AF2" s="8">
+        <f t="shared" ref="AF2:AF17" si="1">Y2+AC2</f>
         <v>97.478999999999985</v>
       </c>
-      <c r="AG2" s="4">
-        <f>SQRT((((H2+I2-$AF2)^2)*T2+((J2+K2-$AF2)^2)*U2+((L2+M2-$AF2)^2)*V2+((N2+O2-$AF2)^2)*W2)/(X2-1))</f>
+      <c r="AG2" s="8">
+        <f t="shared" ref="AG2:AG17" si="2">SQRT((((H2+I2-$AF2)^2)*T2+((J2+K2-$AF2)^2)*U2+((L2+M2-$AF2)^2)*V2+((N2+O2-$AF2)^2)*W2)/(X2-1))</f>
         <v>1.438255192933442</v>
       </c>
       <c r="AH2" s="20">
@@ -15589,7 +17349,7 @@
       </c>
       <c r="AJ2" s="8">
         <f>((H2+I2-$AF$18)^2)*T2+((J2+K2-$AF$18)^2)*U2+((L2+M2-$AF$18)^2)*V2+((N2+O2-$AF$18)^2)*W2</f>
-        <v>551.0699680078128</v>
+        <v>145.84861698208141</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -15599,7 +17359,7 @@
       <c r="B3" s="6">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="7">
         <v>14</v>
       </c>
@@ -15676,45 +17436,45 @@
         <v>4</v>
       </c>
       <c r="Y3" s="8">
-        <f t="shared" ref="Y3:Y17" si="1">(I3*T3+K3*U3+M3*V3+O3*W3)/X3</f>
+        <f t="shared" ref="Y3:Y17" si="3">(I3*T3+K3*U3+M3*V3+O3*W3)/X3</f>
         <v>68.791499999999999</v>
       </c>
       <c r="Z3" s="8">
-        <f t="shared" ref="Z3:Z16" si="2">SQRT((((I3-$Y3)^2)*T3+((K3-$Y3)^2)*U3+((M3-$Y3)^2)*V3+((O3-$Y3)^2)*W3)/(X3-1))</f>
+        <f t="shared" ref="Z3:Z16" si="4">SQRT((((I3-$Y3)^2)*T3+((K3-$Y3)^2)*U3+((M3-$Y3)^2)*V3+((O3-$Y3)^2)*W3)/(X3-1))</f>
         <v>24.734726378110597</v>
       </c>
       <c r="AA3" s="20">
-        <f t="shared" ref="AA3:AA17" si="3">Y3/(Y3+AC3)</f>
+        <f t="shared" ref="AA3:AA17" si="5">Y3/(Y3+AC3)</f>
         <v>0.72529297338330889</v>
       </c>
-      <c r="AB3" s="33"/>
+      <c r="AB3" s="45"/>
       <c r="AC3" s="8">
         <f t="shared" si="0"/>
         <v>26.055</v>
       </c>
       <c r="AD3" s="8">
-        <f>SQRT((((H3-$Z3)^2)*T3+((J3-$Z3)^2)*U3+((L3-$Z3)^2)*V3+((N3-$Z3)^2)*W3)/(X3-1))</f>
+        <f t="shared" ref="AD2:AD17" si="6">SQRT((((H3-$Z3)^2)*T3+((J3-$Z3)^2)*U3+((L3-$Z3)^2)*V3+((N3-$Z3)^2)*W3)/(X3-1))</f>
         <v>5.3080270580391664</v>
       </c>
       <c r="AE3" s="9">
-        <f>AC3/(Y3+AC3)</f>
+        <f t="shared" ref="AE2:AE17" si="7">AC3/(Y3+AC3)</f>
         <v>0.27470702661669122</v>
       </c>
-      <c r="AF3" s="4">
-        <f>Y3+AC3</f>
+      <c r="AF3" s="8">
+        <f t="shared" si="1"/>
         <v>94.846499999999992</v>
       </c>
-      <c r="AG3" s="4">
-        <f>SQRT((((H3+I3-$AF3)^2)*T3+((J3+K3-$AF3)^2)*U3+((L3+M3-$AF3)^2)*V3+((N3+O3-$AF3)^2)*W3)/(X3-1))</f>
+      <c r="AG3" s="8">
+        <f t="shared" si="2"/>
         <v>23.318648009693877</v>
       </c>
       <c r="AH3" s="20">
-        <f t="shared" ref="AH3:AH17" si="4">AG3/AF3</f>
+        <f t="shared" ref="AH3:AH17" si="8">AG3/AF3</f>
         <v>0.24585670541025637</v>
       </c>
       <c r="AJ3" s="8">
-        <f t="shared" ref="AJ3:AJ16" si="5">((H3+I3-$AF$18)^2)*T3+((J3+K3-$AF$18)^2)*U3+((L3+M3-$AF$18)^2)*V3+((N3+O3-$AF$18)^2)*W3</f>
-        <v>3105.9244362656259</v>
+        <f t="shared" ref="AJ3:AJ16" si="9">((H3+I3-$AF$18)^2)*T3+((J3+K3-$AF$18)^2)*U3+((L3+M3-$AF$18)^2)*V3+((N3+O3-$AF$18)^2)*W3</f>
+        <v>2125.1218287699171</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -15724,7 +17484,7 @@
       <c r="B4" s="6">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="7">
         <v>17</v>
       </c>
@@ -15801,45 +17561,45 @@
         <v>2</v>
       </c>
       <c r="Y4" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>165.51900000000001</v>
       </c>
       <c r="Z4" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2600642840744352</v>
       </c>
       <c r="AA4" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.85531578457817881</v>
       </c>
-      <c r="AB4" s="33"/>
+      <c r="AB4" s="45"/>
       <c r="AC4" s="8">
         <f t="shared" si="0"/>
         <v>27.999000000000002</v>
       </c>
       <c r="AD4" s="8">
-        <f>SQRT((((H4-$Z4)^2)*T4+((J4-$Z4)^2)*U4+((L4-$Z4)^2)*V4+((N4-$Z4)^2)*W4)/(X4-1))</f>
+        <f t="shared" si="6"/>
         <v>38.580512288470196</v>
       </c>
       <c r="AE4" s="9">
-        <f>AC4/(Y4+AC4)</f>
+        <f t="shared" si="7"/>
         <v>0.14468421542182125</v>
       </c>
-      <c r="AF4" s="4">
-        <f>Y4+AC4</f>
+      <c r="AF4" s="8">
+        <f t="shared" si="1"/>
         <v>193.518</v>
       </c>
-      <c r="AG4" s="4">
-        <f>SQRT((((H4+I4-$AF4)^2)*T4+((J4+K4-$AF4)^2)*U4+((L4+M4-$AF4)^2)*V4+((N4+O4-$AF4)^2)*W4)/(X4-1))</f>
+      <c r="AG4" s="8">
+        <f t="shared" si="2"/>
         <v>8.9095454429504954</v>
       </c>
       <c r="AH4" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>4.6039879716359693E-2</v>
       </c>
       <c r="AJ4" s="8">
-        <f t="shared" si="5"/>
-        <v>12710.639814257811</v>
+        <f t="shared" si="9"/>
+        <v>15412.957866643277</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -15849,7 +17609,7 @@
       <c r="B5" s="6">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="7">
         <v>20</v>
       </c>
@@ -15930,41 +17690,41 @@
         <v>158.51400000000001</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12.824811577563233</v>
       </c>
       <c r="AA5" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.88425879439033372</v>
       </c>
-      <c r="AB5" s="33"/>
+      <c r="AB5" s="45"/>
       <c r="AC5" s="8">
         <f t="shared" si="0"/>
         <v>20.748000000000001</v>
       </c>
       <c r="AD5" s="8">
-        <f>SQRT((((H5-$Z5)^2)*T5+((J5-$Z5)^2)*U5+((L5-$Z5)^2)*V5+((N5-$Z5)^2)*W5)/(X5-1))</f>
+        <f t="shared" si="6"/>
         <v>9.7212365554055928</v>
       </c>
       <c r="AE5" s="9">
-        <f>AC5/(Y5+AC5)</f>
+        <f t="shared" si="7"/>
         <v>0.1157412056096663</v>
       </c>
-      <c r="AF5" s="4">
-        <f>Y5+AC5</f>
+      <c r="AF5" s="8">
+        <f t="shared" si="1"/>
         <v>179.262</v>
       </c>
-      <c r="AG5" s="4">
-        <f>SQRT((((H5+I5-$AF5)^2)*T5+((J5+K5-$AF5)^2)*U5+((L5+M5-$AF5)^2)*V5+((N5+O5-$AF5)^2)*W5)/(X5-1))</f>
+      <c r="AG5" s="8">
+        <f t="shared" si="2"/>
         <v>12.675489576343782</v>
       </c>
       <c r="AH5" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.0709294643280685E-2</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="5"/>
-        <v>13080.300291386717</v>
+        <f t="shared" si="9"/>
+        <v>16441.854061699058</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -15974,7 +17734,7 @@
       <c r="B6" s="6">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="7">
         <v>23</v>
       </c>
@@ -15989,51 +17749,51 @@
       </c>
       <c r="H6" s="7">
         <f>og!H6*0.18</f>
-        <v>20.663999999999998</v>
+        <v>22.355999999999998</v>
       </c>
       <c r="I6" s="7">
         <f>og!I6*0.18</f>
-        <v>173.142</v>
+        <v>55.008000000000003</v>
       </c>
       <c r="J6" s="7">
         <f>og!J6*0.18</f>
-        <v>21.312000000000001</v>
+        <v>21.276</v>
       </c>
       <c r="K6" s="7">
         <f>og!K6*0.18</f>
-        <v>144.77399999999997</v>
+        <v>85.427999999999997</v>
       </c>
       <c r="L6" s="7">
         <f>og!L6*0.18</f>
-        <v>20.213999999999999</v>
+        <v>17.064</v>
       </c>
       <c r="M6" s="7">
         <f>og!M6*0.18</f>
-        <v>153.19800000000001</v>
+        <v>100.72799999999999</v>
       </c>
       <c r="N6" s="7">
         <f>og!N6*0.18</f>
-        <v>21.366</v>
+        <v>19.89</v>
       </c>
       <c r="O6" s="7">
         <f>og!O6*0.18</f>
-        <v>149.202</v>
+        <v>60.713999999999999</v>
       </c>
       <c r="P6" s="7">
         <f>og!P6*0.18</f>
-        <v>193.82399999999998</v>
+        <v>77.381999999999991</v>
       </c>
       <c r="Q6" s="7">
         <f>og!Q6*0.18</f>
-        <v>166.08600000000001</v>
+        <v>106.70399999999999</v>
       </c>
       <c r="R6" s="7">
         <f>og!R6*0.18</f>
-        <v>173.41199999999998</v>
+        <v>117.77399999999999</v>
       </c>
       <c r="S6" s="7">
         <f>og!S6*0.18</f>
-        <v>170.56799999999998</v>
+        <v>80.603999999999999</v>
       </c>
       <c r="T6" s="7">
         <v>1</v>
@@ -16051,45 +17811,45 @@
         <v>3</v>
       </c>
       <c r="Y6" s="8">
-        <f t="shared" si="1"/>
-        <v>158.51400000000001</v>
+        <f t="shared" si="3"/>
+        <v>72.149999999999991</v>
       </c>
       <c r="Z6" s="8">
-        <f t="shared" si="2"/>
-        <v>12.824811577563233</v>
+        <f t="shared" si="4"/>
+        <v>24.913172660261477</v>
       </c>
       <c r="AA6" s="20">
-        <f t="shared" si="3"/>
-        <v>0.88425879439033372</v>
-      </c>
-      <c r="AB6" s="33"/>
+        <f t="shared" si="5"/>
+        <v>0.78492167101827681</v>
+      </c>
+      <c r="AB6" s="45"/>
       <c r="AC6" s="8">
         <f t="shared" si="0"/>
-        <v>20.748000000000001</v>
+        <v>19.77</v>
       </c>
       <c r="AD6" s="8">
-        <f>SQRT((((H6-$Z6)^2)*T6+((J6-$Z6)^2)*U6+((L6-$Z6)^2)*V6+((N6-$Z6)^2)*W6)/(X6-1))</f>
-        <v>9.7212365554055928</v>
+        <f t="shared" si="6"/>
+        <v>6.8330413082237165</v>
       </c>
       <c r="AE6" s="9">
-        <f>AC6/(Y6+AC6)</f>
-        <v>0.1157412056096663</v>
-      </c>
-      <c r="AF6" s="4">
-        <f>Y6+AC6</f>
-        <v>179.262</v>
-      </c>
-      <c r="AG6" s="4">
-        <f>SQRT((((H6+I6-$AF6)^2)*T6+((J6+K6-$AF6)^2)*U6+((L6+M6-$AF6)^2)*V6+((N6+O6-$AF6)^2)*W6)/(X6-1))</f>
-        <v>12.675489576343782</v>
+        <f t="shared" si="7"/>
+        <v>0.21507832898172327</v>
+      </c>
+      <c r="AF6" s="8">
+        <f t="shared" si="1"/>
+        <v>91.919999999999987</v>
+      </c>
+      <c r="AG6" s="8">
+        <f t="shared" si="2"/>
+        <v>22.464298074945496</v>
       </c>
       <c r="AH6" s="20">
-        <f t="shared" si="4"/>
-        <v>7.0709294643280685E-2</v>
+        <f t="shared" si="8"/>
+        <v>0.24438966574135662</v>
       </c>
       <c r="AJ6" s="8">
-        <f t="shared" si="5"/>
-        <v>13080.300291386717</v>
+        <f t="shared" si="9"/>
+        <v>1600.4687137663368</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -16099,7 +17859,7 @@
       <c r="B7" s="6">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="7">
         <v>2</v>
       </c>
@@ -16114,51 +17874,51 @@
       </c>
       <c r="H7" s="7">
         <f>og!H7*0.18</f>
-        <v>22.355999999999998</v>
+        <v>23.200969903516619</v>
       </c>
       <c r="I7" s="7">
         <f>og!I7*0.18</f>
-        <v>55.008000000000003</v>
+        <v>36.186965990953198</v>
       </c>
       <c r="J7" s="7">
         <f>og!J7*0.18</f>
-        <v>21.276</v>
+        <v>17.654829000849126</v>
       </c>
       <c r="K7" s="7">
         <f>og!K7*0.18</f>
-        <v>85.427999999999997</v>
+        <v>50.812106682649137</v>
       </c>
       <c r="L7" s="7">
         <f>og!L7*0.18</f>
-        <v>17.064</v>
+        <v>23.235444570238201</v>
       </c>
       <c r="M7" s="7">
         <f>og!M7*0.18</f>
-        <v>100.72799999999999</v>
+        <v>41.372883988196939</v>
       </c>
       <c r="N7" s="7">
         <f>og!N7*0.18</f>
-        <v>19.89</v>
+        <v>21.655886832648896</v>
       </c>
       <c r="O7" s="7">
         <f>og!O7*0.18</f>
-        <v>60.713999999999999</v>
+        <v>0</v>
       </c>
       <c r="P7" s="7">
         <f>og!P7*0.18</f>
-        <v>77.381999999999991</v>
+        <v>59.38793589446982</v>
       </c>
       <c r="Q7" s="7">
         <f>og!Q7*0.18</f>
-        <v>106.70399999999999</v>
+        <v>68.466935683498264</v>
       </c>
       <c r="R7" s="7">
         <f>og!R7*0.18</f>
-        <v>117.77399999999999</v>
+        <v>64.608328558435147</v>
       </c>
       <c r="S7" s="7">
         <f>og!S7*0.18</f>
-        <v>80.603999999999999</v>
+        <v>63.028770820845843</v>
       </c>
       <c r="T7" s="7">
         <v>1</v>
@@ -16176,45 +17936,45 @@
         <v>4</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" si="1"/>
-        <v>75.469499999999996</v>
+        <f t="shared" si="3"/>
+        <v>32.092989165449822</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="2"/>
-        <v>21.397517823336422</v>
+        <f t="shared" si="4"/>
+        <v>22.235425251651964</v>
       </c>
       <c r="AA7" s="20">
-        <f t="shared" si="3"/>
-        <v>0.78929781626506024</v>
-      </c>
-      <c r="AB7" s="33"/>
+        <f t="shared" si="5"/>
+        <v>0.59953532624746175</v>
+      </c>
+      <c r="AB7" s="45"/>
       <c r="AC7" s="8">
         <f t="shared" si="0"/>
-        <v>20.1465</v>
+        <v>21.436782576813208</v>
       </c>
       <c r="AD7" s="8">
-        <f>SQRT((((H7-$Z7)^2)*T7+((J7-$Z7)^2)*U7+((L7-$Z7)^2)*V7+((N7-$Z7)^2)*W7)/(X7-1))</f>
-        <v>2.707116631967279</v>
+        <f t="shared" si="6"/>
+        <v>2.7838846901562877</v>
       </c>
       <c r="AE7" s="9">
-        <f>AC7/(Y7+AC7)</f>
-        <v>0.21070218373493976</v>
-      </c>
-      <c r="AF7" s="4">
-        <f>Y7+AC7</f>
-        <v>95.616</v>
-      </c>
-      <c r="AG7" s="4">
-        <f>SQRT((((H7+I7-$AF7)^2)*T7+((J7+K7-$AF7)^2)*U7+((L7+M7-$AF7)^2)*V7+((N7+O7-$AF7)^2)*W7)/(X7-1))</f>
-        <v>19.775526693365212</v>
+        <f t="shared" si="7"/>
+        <v>0.4004646737525383</v>
+      </c>
+      <c r="AF7" s="8">
+        <f t="shared" si="1"/>
+        <v>53.52977174226303</v>
+      </c>
+      <c r="AG7" s="8">
+        <f t="shared" si="2"/>
+        <v>21.572481809024048</v>
       </c>
       <c r="AH7" s="20">
-        <f t="shared" si="4"/>
-        <v>0.20682235915919106</v>
+        <f t="shared" si="8"/>
+        <v>0.40299969730661228</v>
       </c>
       <c r="AJ7" s="8">
-        <f t="shared" si="5"/>
-        <v>2532.0306275156245</v>
+        <f t="shared" si="9"/>
+        <v>12390.907761429578</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -16224,7 +17984,7 @@
       <c r="B8" s="6">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="7">
         <v>5</v>
       </c>
@@ -16301,45 +18061,45 @@
         <v>3</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25.913999999999998</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.5726015468540364</v>
       </c>
       <c r="AA8" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.52307133341407286</v>
       </c>
-      <c r="AB8" s="33"/>
+      <c r="AB8" s="45"/>
       <c r="AC8" s="8">
         <f t="shared" si="0"/>
         <v>23.628</v>
       </c>
       <c r="AD8" s="8">
-        <f>SQRT((((H8-$Z8)^2)*T8+((J8-$Z8)^2)*U8+((L8-$Z8)^2)*V8+((N8-$Z8)^2)*W8)/(X8-1))</f>
+        <f t="shared" si="6"/>
         <v>22.17672771066098</v>
       </c>
       <c r="AE8" s="9">
-        <f>AC8/(Y8+AC8)</f>
+        <f t="shared" si="7"/>
         <v>0.47692866658592709</v>
       </c>
-      <c r="AF8" s="4">
-        <f>Y8+AC8</f>
+      <c r="AF8" s="8">
+        <f t="shared" si="1"/>
         <v>49.542000000000002</v>
       </c>
-      <c r="AG8" s="4">
-        <f>SQRT((((H8+I8-$AF8)^2)*T8+((J8+K8-$AF8)^2)*U8+((L8+M8-$AF8)^2)*V8+((N8+O8-$AF8)^2)*W8)/(X8-1))</f>
+      <c r="AG8" s="8">
+        <f t="shared" si="2"/>
         <v>7.1632838838063622</v>
       </c>
       <c r="AH8" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.14459012320468212</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="5"/>
-        <v>12585.334536386719</v>
+        <f t="shared" si="9"/>
+        <v>9650.8521431014451</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -16349,7 +18109,7 @@
       <c r="B9" s="6">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="7">
         <v>8</v>
       </c>
@@ -16426,45 +18186,45 @@
         <v>3</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.0839999999999996</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9642280926613378</v>
       </c>
       <c r="AA9" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.22832695338887635</v>
       </c>
-      <c r="AB9" s="33"/>
+      <c r="AB9" s="45"/>
       <c r="AC9" s="8">
         <f t="shared" si="0"/>
         <v>20.562000000000001</v>
       </c>
       <c r="AD9" s="8">
-        <f>SQRT((((H9-$Z9)^2)*T9+((J9-$Z9)^2)*U9+((L9-$Z9)^2)*V9+((N9-$Z9)^2)*W9)/(X9-1))</f>
+        <f t="shared" si="6"/>
         <v>22.803004273035885</v>
       </c>
       <c r="AE9" s="9">
-        <f>AC9/(Y9+AC9)</f>
+        <f t="shared" si="7"/>
         <v>0.77167304661112368</v>
       </c>
-      <c r="AF9" s="4">
-        <f>Y9+AC9</f>
+      <c r="AF9" s="8">
+        <f t="shared" si="1"/>
         <v>26.646000000000001</v>
       </c>
-      <c r="AG9" s="4">
-        <f>SQRT((((H9+I9-$AF9)^2)*T9+((J9+K9-$AF9)^2)*U9+((L9+M9-$AF9)^2)*V9+((N9+O9-$AF9)^2)*W9)/(X9-1))</f>
+      <c r="AG9" s="8">
+        <f t="shared" si="2"/>
         <v>1.7719108329710043</v>
       </c>
       <c r="AH9" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.6498192335472647E-2</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="5"/>
-        <v>22923.116514386715</v>
+        <f>((H9+I9-$AF$18)^2)*T9+((J9+K9-$AF$18)^2)*U9+((L9+M9-$AF$18)^2)*V9+((N9+O9-$AF$18)^2)*W9</f>
+        <v>18877.363353280518</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -16474,7 +18234,7 @@
       <c r="B10" s="11">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="50">
         <v>209</v>
       </c>
       <c r="D10" s="12">
@@ -16553,18 +18313,18 @@
         <v>2</v>
       </c>
       <c r="Y10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.32</v>
       </c>
       <c r="Z10" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.0402571362977113</v>
       </c>
       <c r="AA10" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39215686274509809</v>
       </c>
-      <c r="AB10" s="34">
+      <c r="AB10" s="46">
         <f>AVERAGE(AA10:AA11)</f>
         <v>0.55819895006057352</v>
       </c>
@@ -16573,28 +18333,28 @@
         <v>34.595999999999997</v>
       </c>
       <c r="AD10" s="13">
-        <f>SQRT((((H10-$Z10)^2)*T10+((J10-$Z10)^2)*U10+((L10-$Z10)^2)*V10+((N10-$Z10)^2)*W10)/(X10-1))</f>
+        <f t="shared" si="6"/>
         <v>42.110137977102106</v>
       </c>
       <c r="AE10" s="14">
-        <f>AC10/(Y10+AC10)</f>
+        <f t="shared" si="7"/>
         <v>0.60784313725490191</v>
       </c>
       <c r="AF10" s="13">
-        <f>Y10+AC10</f>
+        <f t="shared" si="1"/>
         <v>56.915999999999997</v>
       </c>
       <c r="AG10" s="13">
-        <f>SQRT((((H10+I10-$AF10)^2)*T10+((J10+K10-$AF10)^2)*U10+((L10+M10-$AF10)^2)*V10+((N10+O10-$AF10)^2)*W10)/(X10-1))</f>
+        <f t="shared" si="2"/>
         <v>7.6367532368150026E-2</v>
       </c>
       <c r="AH10" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.3417585980769911E-3</v>
       </c>
-      <c r="AJ10" s="8">
-        <f t="shared" si="5"/>
-        <v>6527.9224367578117</v>
+      <c r="AJ10" s="13">
+        <f t="shared" si="9"/>
+        <v>4810.2017800274352</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -16604,7 +18364,7 @@
       <c r="B11" s="11">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="12">
         <v>13</v>
       </c>
@@ -16681,425 +18441,425 @@
         <v>4</v>
       </c>
       <c r="Y11" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>106.81649999999999</v>
       </c>
       <c r="Z11" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>51.976427512863935</v>
       </c>
       <c r="AA11" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.72424103737604884</v>
       </c>
-      <c r="AB11" s="34"/>
+      <c r="AB11" s="46"/>
       <c r="AC11" s="13">
         <f t="shared" si="0"/>
         <v>40.670999999999992</v>
       </c>
       <c r="AD11" s="13">
-        <f>SQRT((((H11-$Z11)^2)*T11+((J11-$Z11)^2)*U11+((L11-$Z11)^2)*V11+((N11-$Z11)^2)*W11)/(X11-1))</f>
+        <f t="shared" si="6"/>
         <v>14.726433025849397</v>
       </c>
       <c r="AE11" s="14">
-        <f>AC11/(Y11+AC11)</f>
+        <f t="shared" si="7"/>
         <v>0.27575896262395116</v>
       </c>
       <c r="AF11" s="13">
-        <f>Y11+AC11</f>
+        <f t="shared" si="1"/>
         <v>147.48749999999998</v>
       </c>
       <c r="AG11" s="13">
-        <f>SQRT((((H11+I11-$AF11)^2)*T11+((J11+K11-$AF11)^2)*U11+((L11+M11-$AF11)^2)*V11+((N11+O11-$AF11)^2)*W11)/(X11-1))</f>
+        <f t="shared" si="2"/>
         <v>53.825823848780985</v>
       </c>
       <c r="AH11" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.36495176776866506</v>
       </c>
-      <c r="AJ11" s="8">
-        <f t="shared" si="5"/>
-        <v>13164.709379765625</v>
+      <c r="AJ11" s="13">
+        <f t="shared" si="9"/>
+        <v>15590.522454127682</v>
       </c>
     </row>
-    <row r="12" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+    <row r="12" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="34">
         <v>37198</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="35">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="51">
         <v>236</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="36">
         <v>8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="36">
         <v>236.33333300000001</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="34">
         <v>44797</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="36">
         <f>og!H12*0.18</f>
         <v>15.803999999999998</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="36">
         <f>og!I12*0.18</f>
         <v>185.85</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="36">
         <f>og!J12*0.18</f>
         <v>15.012</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="36">
         <f>og!K12*0.18</f>
         <v>-0.70199999999999996</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="36">
         <f>og!L12*0.18</f>
         <v>14.237999999999998</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="36">
         <f>og!M12*0.18</f>
         <v>113.202</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="36">
         <f>og!N12*0.18</f>
         <v>15.606</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="36">
         <f>og!O12*0.18</f>
         <v>88.83</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12" s="36">
         <f>og!P12*0.18</f>
         <v>201.654</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="Q12" s="36">
         <f>og!Q12*0.18</f>
         <v>14.292</v>
       </c>
-      <c r="R12" s="24">
+      <c r="R12" s="36">
         <f>og!R12*0.18</f>
         <v>127.44</v>
       </c>
-      <c r="S12" s="24">
+      <c r="S12" s="36">
         <f>og!S12*0.18</f>
         <v>104.43600000000001</v>
       </c>
-      <c r="T12" s="24">
-        <v>1</v>
-      </c>
-      <c r="U12" s="24">
+      <c r="T12" s="36">
+        <v>1</v>
+      </c>
+      <c r="U12" s="36">
         <v>0</v>
       </c>
-      <c r="V12" s="24">
-        <v>1</v>
-      </c>
-      <c r="W12" s="24">
-        <v>1</v>
-      </c>
-      <c r="X12" s="24">
+      <c r="V12" s="36">
+        <v>1</v>
+      </c>
+      <c r="W12" s="36">
+        <v>1</v>
+      </c>
+      <c r="X12" s="36">
         <v>3</v>
       </c>
-      <c r="Y12" s="25">
-        <f t="shared" si="1"/>
+      <c r="Y12" s="38">
+        <f t="shared" si="3"/>
         <v>129.29400000000001</v>
       </c>
-      <c r="Z12" s="25">
-        <f t="shared" si="2"/>
+      <c r="Z12" s="38">
+        <f t="shared" si="4"/>
         <v>50.472115549083142</v>
       </c>
-      <c r="AA12" s="27">
-        <f t="shared" si="3"/>
+      <c r="AA12" s="44">
+        <f t="shared" si="5"/>
         <v>0.89470624870251192</v>
       </c>
-      <c r="AB12" s="35">
+      <c r="AB12" s="47">
         <f>AVERAGE(AA12:AA14)</f>
         <v>0.92088309745456287</v>
       </c>
-      <c r="AC12" s="25">
+      <c r="AC12" s="38">
         <f t="shared" si="0"/>
         <v>15.215999999999999</v>
       </c>
-      <c r="AD12" s="25">
-        <f>SQRT((((H12-$Z12)^2)*T12+((J12-$Z12)^2)*U12+((L12-$Z12)^2)*V12+((N12-$Z12)^2)*W12)/(X12-1))</f>
+      <c r="AD12" s="38">
+        <f t="shared" si="6"/>
         <v>43.188166080715362</v>
       </c>
-      <c r="AE12" s="26">
-        <f>AC12/(Y12+AC12)</f>
+      <c r="AE12" s="37">
+        <f t="shared" si="7"/>
         <v>0.10529375129748804</v>
       </c>
-      <c r="AF12" s="25">
-        <f>Y12+AC12</f>
+      <c r="AF12" s="38">
+        <f t="shared" si="1"/>
         <v>144.51000000000002</v>
       </c>
-      <c r="AG12" s="25">
-        <f>SQRT((((H12+I12-$AF12)^2)*T12+((J12+K12-$AF12)^2)*U12+((L12+M12-$AF12)^2)*V12+((N12+O12-$AF12)^2)*W12)/(X12-1))</f>
+      <c r="AG12" s="38">
+        <f t="shared" si="2"/>
         <v>50.807219526362594</v>
       </c>
-      <c r="AH12" s="27">
-        <f t="shared" si="4"/>
+      <c r="AH12" s="44">
+        <f t="shared" si="8"/>
         <v>0.35158272456136314</v>
       </c>
-      <c r="AJ12" s="8">
-        <f t="shared" si="5"/>
-        <v>7946.7187953867187</v>
+      <c r="AJ12" s="38">
+        <f t="shared" si="9"/>
+        <v>9621.5638950442317</v>
       </c>
     </row>
-    <row r="13" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22">
+    <row r="13" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34">
         <v>37563</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="35">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="24">
+      <c r="C13" s="51"/>
+      <c r="D13" s="36">
         <v>13</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="36">
         <v>236.54166699999999</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="34">
         <v>44797</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="36">
         <f>og!H13*0.18</f>
         <v>15.696</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="36">
         <f>og!I13*0.18</f>
         <v>212.184</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="36">
         <f>og!J13*0.18</f>
         <v>12.473999999999998</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="36">
         <f>og!K13*0.18</f>
         <v>195.39</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="36">
         <f>og!L13*0.18</f>
         <v>19.8</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13" s="36">
         <f>og!M13*0.18</f>
         <v>171.61199999999999</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="36">
         <f>og!N13*0.18</f>
         <v>13.752000000000001</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="36">
         <f>og!O13*0.18</f>
         <v>201.27600000000001</v>
       </c>
-      <c r="P13" s="24">
+      <c r="P13" s="36">
         <f>og!P13*0.18</f>
         <v>227.88</v>
       </c>
-      <c r="Q13" s="24">
+      <c r="Q13" s="36">
         <f>og!Q13*0.18</f>
         <v>207.88200000000001</v>
       </c>
-      <c r="R13" s="24">
+      <c r="R13" s="36">
         <f>og!R13*0.18</f>
         <v>191.41200000000001</v>
       </c>
-      <c r="S13" s="24">
+      <c r="S13" s="36">
         <f>og!S13*0.18</f>
         <v>215.02799999999996</v>
       </c>
-      <c r="T13" s="24">
-        <v>1</v>
-      </c>
-      <c r="U13" s="24">
-        <v>1</v>
-      </c>
-      <c r="V13" s="24">
-        <v>1</v>
-      </c>
-      <c r="W13" s="24">
-        <v>1</v>
-      </c>
-      <c r="X13" s="24">
+      <c r="T13" s="36">
+        <v>1</v>
+      </c>
+      <c r="U13" s="36">
+        <v>1</v>
+      </c>
+      <c r="V13" s="36">
+        <v>1</v>
+      </c>
+      <c r="W13" s="36">
+        <v>1</v>
+      </c>
+      <c r="X13" s="36">
         <v>4</v>
       </c>
-      <c r="Y13" s="25">
-        <f t="shared" si="1"/>
+      <c r="Y13" s="38">
+        <f t="shared" si="3"/>
         <v>195.1155</v>
       </c>
-      <c r="Z13" s="25">
-        <f t="shared" si="2"/>
+      <c r="Z13" s="38">
+        <f t="shared" si="4"/>
         <v>17.144244077823906</v>
       </c>
-      <c r="AA13" s="27">
-        <f t="shared" si="3"/>
+      <c r="AA13" s="44">
+        <f t="shared" si="5"/>
         <v>0.92671197743011036</v>
       </c>
-      <c r="AB13" s="35"/>
-      <c r="AC13" s="25">
+      <c r="AB13" s="47"/>
+      <c r="AC13" s="38">
         <f t="shared" si="0"/>
         <v>15.4305</v>
       </c>
-      <c r="AD13" s="25">
-        <f>SQRT((((H13-$Z13)^2)*T13+((J13-$Z13)^2)*U13+((L13-$Z13)^2)*V13+((N13-$Z13)^2)*W13)/(X13-1))</f>
+      <c r="AD13" s="38">
+        <f t="shared" si="6"/>
         <v>3.7624880977488844</v>
       </c>
-      <c r="AE13" s="26">
-        <f>AC13/(Y13+AC13)</f>
+      <c r="AE13" s="37">
+        <f t="shared" si="7"/>
         <v>7.3288022569889713E-2</v>
       </c>
-      <c r="AF13" s="25">
-        <f>Y13+AC13</f>
+      <c r="AF13" s="38">
+        <f t="shared" si="1"/>
         <v>210.54599999999999</v>
       </c>
-      <c r="AG13" s="25">
-        <f>SQRT((((H13+I13-$AF13)^2)*T13+((J13+K13-$AF13)^2)*U13+((L13+M13-$AF13)^2)*V13+((N13+O13-$AF13)^2)*W13)/(X13-1))</f>
+      <c r="AG13" s="38">
+        <f t="shared" si="2"/>
         <v>15.208100473103141</v>
       </c>
-      <c r="AH13" s="27">
-        <f t="shared" si="4"/>
+      <c r="AH13" s="44">
+        <f t="shared" si="8"/>
         <v>7.2231723581085094E-2</v>
       </c>
-      <c r="AJ13" s="8">
-        <f t="shared" si="5"/>
-        <v>37942.038714515627</v>
+      <c r="AJ13" s="38">
+        <f>((H13+I13-$AF$18)^2)*T13+((J13+K13-$AF$18)^2)*U13+((L13+M13-$AF$18)^2)*V13+((N13+O13-$AF$18)^2)*W13</f>
+        <v>44448.626754672936</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+    <row r="14" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="34">
         <v>37928</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="35">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="24">
+      <c r="C14" s="51"/>
+      <c r="D14" s="36">
         <v>20</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="36">
         <v>236.83333300000001</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="34">
         <v>44797</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="36">
         <f>og!H14*0.18</f>
         <v>15.03</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="36">
         <f>og!I14*0.18</f>
         <v>292.10399999999998</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="36">
         <f>og!J14*0.18</f>
         <v>15.623999999999999</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="36">
         <f>og!K14*0.18</f>
         <v>211.41</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="36">
         <f>og!L14*0.18</f>
         <v>12.33</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14" s="36">
         <f>og!M14*0.18</f>
         <v>215.44200000000001</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14" s="36">
         <f>og!N14*0.18</f>
         <v>14.004</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="36">
         <f>og!O14*0.18</f>
         <v>193.75200000000001</v>
       </c>
-      <c r="P14" s="24">
+      <c r="P14" s="36">
         <f>og!P14*0.18</f>
         <v>307.11599999999999</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="Q14" s="36">
         <f>og!Q14*0.18</f>
         <v>227.03399999999999</v>
       </c>
-      <c r="R14" s="24">
+      <c r="R14" s="36">
         <f>og!R14*0.18</f>
         <v>227.77200000000002</v>
       </c>
-      <c r="S14" s="24">
+      <c r="S14" s="36">
         <f>og!S14*0.18</f>
         <v>207.756</v>
       </c>
-      <c r="T14" s="24">
-        <v>1</v>
-      </c>
-      <c r="U14" s="24">
-        <v>1</v>
-      </c>
-      <c r="V14" s="24">
-        <v>1</v>
-      </c>
-      <c r="W14" s="24">
-        <v>1</v>
-      </c>
-      <c r="X14" s="24">
+      <c r="T14" s="36">
+        <v>1</v>
+      </c>
+      <c r="U14" s="36">
+        <v>1</v>
+      </c>
+      <c r="V14" s="36">
+        <v>1</v>
+      </c>
+      <c r="W14" s="36">
+        <v>1</v>
+      </c>
+      <c r="X14" s="36">
         <v>4</v>
       </c>
-      <c r="Y14" s="25">
-        <f t="shared" si="1"/>
+      <c r="Y14" s="38">
+        <f t="shared" si="3"/>
         <v>228.17700000000002</v>
       </c>
-      <c r="Z14" s="25">
-        <f t="shared" si="2"/>
+      <c r="Z14" s="38">
+        <f t="shared" si="4"/>
         <v>43.646513675206627</v>
       </c>
-      <c r="AA14" s="27">
-        <f t="shared" si="3"/>
+      <c r="AA14" s="44">
+        <f t="shared" si="5"/>
         <v>0.94123106623106634</v>
       </c>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="25">
+      <c r="AB14" s="47"/>
+      <c r="AC14" s="38">
         <f t="shared" si="0"/>
         <v>14.246999999999998</v>
       </c>
-      <c r="AD14" s="25">
-        <f>SQRT((((H14-$Z14)^2)*T14+((J14-$Z14)^2)*U14+((L14-$Z14)^2)*V14+((N14-$Z14)^2)*W14)/(X14-1))</f>
+      <c r="AD14" s="38">
+        <f t="shared" si="6"/>
         <v>33.978271357612485</v>
       </c>
-      <c r="AE14" s="26">
-        <f>AC14/(Y14+AC14)</f>
+      <c r="AE14" s="37">
+        <f t="shared" si="7"/>
         <v>5.8768933768933759E-2</v>
       </c>
-      <c r="AF14" s="25">
-        <f>Y14+AC14</f>
+      <c r="AF14" s="38">
+        <f t="shared" si="1"/>
         <v>242.42400000000001</v>
       </c>
-      <c r="AG14" s="25">
-        <f>SQRT((((H14+I14-$AF14)^2)*T14+((J14+K14-$AF14)^2)*U14+((L14+M14-$AF14)^2)*V14+((N14+O14-$AF14)^2)*W14)/(X14-1))</f>
+      <c r="AG14" s="38">
+        <f t="shared" si="2"/>
         <v>44.124020397058082</v>
       </c>
-      <c r="AH14" s="27">
-        <f t="shared" si="4"/>
+      <c r="AH14" s="44">
+        <f t="shared" si="8"/>
         <v>0.18201176614963074</v>
       </c>
-      <c r="AJ14" s="8">
-        <f t="shared" si="5"/>
-        <v>71763.339855515616</v>
+      <c r="AJ14" s="38">
+        <f t="shared" si="9"/>
+        <v>80332.88442587301</v>
       </c>
     </row>
     <row r="15" spans="1:36" s="17" customFormat="1" x14ac:dyDescent="0.2">
@@ -17109,7 +18869,7 @@
       <c r="B15" s="16">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="52">
         <v>258</v>
       </c>
       <c r="D15" s="17">
@@ -17188,18 +18948,18 @@
         <v>3</v>
       </c>
       <c r="Y15" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>34.379999999999995</v>
       </c>
       <c r="Z15" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10.928075585390138</v>
       </c>
       <c r="AA15" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.74804177545691908</v>
       </c>
-      <c r="AB15" s="36">
+      <c r="AB15" s="48">
         <f>AVERAGE(AA15:AA17)</f>
         <v>0.63982732890266025</v>
       </c>
@@ -17208,28 +18968,28 @@
         <v>11.579999999999998</v>
       </c>
       <c r="AD15" s="18">
-        <f>SQRT((((H15-$Z15)^2)*T15+((J15-$Z15)^2)*U15+((L15-$Z15)^2)*V15+((N15-$Z15)^2)*W15)/(X15-1))</f>
+        <f t="shared" si="6"/>
         <v>1.1928923520362666</v>
       </c>
       <c r="AE15" s="19">
-        <f>AC15/(Y15+AC15)</f>
+        <f t="shared" si="7"/>
         <v>0.25195822454308092</v>
       </c>
       <c r="AF15" s="18">
-        <f>Y15+AC15</f>
+        <f t="shared" si="1"/>
         <v>45.959999999999994</v>
       </c>
       <c r="AG15" s="18">
-        <f>SQRT((((H15+I15-$AF15)^2)*T15+((J15+K15-$AF15)^2)*U15+((L15+M15-$AF15)^2)*V15+((N15+O15-$AF15)^2)*W15)/(X15-1))</f>
+        <f t="shared" si="2"/>
         <v>10.88129900333595</v>
       </c>
       <c r="AH15" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.23675585298816257</v>
       </c>
-      <c r="AJ15" s="8">
-        <f t="shared" si="5"/>
-        <v>14144.349575636719</v>
+      <c r="AJ15" s="18">
+        <f t="shared" si="9"/>
+        <v>11036.01271474424</v>
       </c>
     </row>
     <row r="16" spans="1:36" s="17" customFormat="1" x14ac:dyDescent="0.2">
@@ -17239,7 +18999,7 @@
       <c r="B16" s="16">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C16" s="32"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="17">
         <v>13</v>
       </c>
@@ -17316,45 +19076,45 @@
         <v>3</v>
       </c>
       <c r="Y16" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.001999999999999</v>
       </c>
       <c r="Z16" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13.741374167091152</v>
       </c>
       <c r="AA16" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.62673047342334653</v>
       </c>
-      <c r="AB16" s="36"/>
+      <c r="AB16" s="48"/>
       <c r="AC16" s="18">
         <f t="shared" si="0"/>
         <v>13.103999999999999</v>
       </c>
       <c r="AD16" s="18">
-        <f>SQRT((((H16-$Z16)^2)*T16+((J16-$Z16)^2)*U16+((L16-$Z16)^2)*V16+((N16-$Z16)^2)*W16)/(X16-1))</f>
+        <f t="shared" si="6"/>
         <v>1.7155584348289368</v>
       </c>
       <c r="AE16" s="19">
-        <f>AC16/(Y16+AC16)</f>
+        <f t="shared" si="7"/>
         <v>0.37326952657665358</v>
       </c>
       <c r="AF16" s="18">
-        <f>Y16+AC16</f>
+        <f t="shared" si="1"/>
         <v>35.105999999999995</v>
       </c>
       <c r="AG16" s="18">
-        <f>SQRT((((H16+I16-$AF16)^2)*T16+((J16+K16-$AF16)^2)*U16+((L16+M16-$AF16)^2)*V16+((N16+O16-$AF16)^2)*W16)/(X16-1))</f>
+        <f t="shared" si="2"/>
         <v>12.23936910138754</v>
       </c>
       <c r="AH16" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.34864037775273576</v>
       </c>
-      <c r="AJ16" s="8">
-        <f t="shared" si="5"/>
-        <v>18994.678357886714</v>
+      <c r="AJ16" s="18">
+        <f t="shared" si="9"/>
+        <v>15359.536250928184</v>
       </c>
     </row>
     <row r="17" spans="1:36" s="17" customFormat="1" x14ac:dyDescent="0.2">
@@ -17364,7 +19124,7 @@
       <c r="B17" s="16">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="17">
         <v>20</v>
       </c>
@@ -17441,7 +19201,7 @@
         <v>3</v>
       </c>
       <c r="Y17" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13.961999999999998</v>
       </c>
       <c r="Z17" s="18">
@@ -17449,47 +19209,64 @@
         <v>12.640823865555598</v>
       </c>
       <c r="AA17" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.54470973782771537</v>
       </c>
-      <c r="AB17" s="36"/>
+      <c r="AB17" s="48"/>
       <c r="AC17" s="18">
         <f t="shared" si="0"/>
         <v>11.67</v>
       </c>
       <c r="AD17" s="18">
-        <f>SQRT((((H17-$Z17)^2)*T17+((J17-$Z17)^2)*U17+((L17-$Z17)^2)*V17+((N17-$Z17)^2)*W17)/(X17-1))</f>
+        <f t="shared" si="6"/>
         <v>1.6672853585689729</v>
       </c>
       <c r="AE17" s="19">
-        <f>AC17/(Y17+AC17)</f>
+        <f t="shared" si="7"/>
         <v>0.45529026217228469</v>
       </c>
       <c r="AF17" s="18">
-        <f>Y17+AC17</f>
+        <f t="shared" si="1"/>
         <v>25.631999999999998</v>
       </c>
       <c r="AG17" s="18">
-        <f>SQRT((((H17+I17-$AF17)^2)*T17+((J17+K17-$AF17)^2)*U17+((L17+M17-$AF17)^2)*V17+((N17+O17-$AF17)^2)*W17)/(X17-1))</f>
+        <f t="shared" si="2"/>
         <v>12.140609704623568</v>
       </c>
       <c r="AH17" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.47365050345753623</v>
       </c>
-      <c r="AJ17" s="8">
+      <c r="AJ17" s="18">
         <f>((H17+I17-$AF$18)^2)*T17+((J17+K17-$AF$18)^2)*U17+((L17+M17-$AF$18)^2)*V17+((N17+O17-$AF$18)^2)*W17</f>
-        <v>23746.458638636715</v>
+        <v>19651.490393735512</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="Y18" s="4">
+        <f>AVERAGE(Y2:Y17)</f>
+        <v>83.46434307284062</v>
+      </c>
+      <c r="Z18" s="4">
+        <f>AVERAGE(Z2:Z17)</f>
+        <v>18.748317998920193</v>
+      </c>
+      <c r="AC18" s="4">
+        <f>AVERAGE(AC2:AC17)</f>
+        <v>22.493455161050825</v>
+      </c>
+      <c r="AD18" s="4">
+        <f>AVERAGE(AD2:AD17)</f>
+        <v>19.398553608621217</v>
+      </c>
       <c r="AF18" s="18">
         <f>AVERAGE(AF2:AF17)</f>
-        <v>114.0470625</v>
-      </c>
+        <v>105.95779823389144</v>
+      </c>
+      <c r="AG18" s="18"/>
       <c r="AJ18" s="8">
         <f>SQRT(SUM(AJ2:AJ17)/(SUM(X2:X17)-1))</f>
-        <v>74.887525490945734</v>
+        <v>75.254156169016497</v>
       </c>
     </row>
   </sheetData>
